--- a/docs/historico_fma.xlsx
+++ b/docs/historico_fma.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em 15/10/2026 às 09:26 (Brasília). Uma aba por município.</t>
+          <t>Gerado em 15/10/2026 às 09:52 (Brasília). Uma aba por município.</t>
         </is>
       </c>
     </row>
@@ -534,12 +534,19 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Dias sem umidade às 13h aparecem como Sem dado. A coluna aviso indica chuva ausente (assumida 0 mm).</t>
+          <t>Referência dos limites das classes: SOARES, R. V. Determinação de um índice de perigo de incêndio para a região centro paranaense, Brasil. Turrialba, Costa Rica, CATIE/IICA. 72 p. (Tese de Mestrado). 1972.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Dias sem umidade às 13h aparecem como Sem dado. A coluna aviso indica chuva ausente (assumida 0 mm).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>A FMA é acumulativa: no início da série o valor pode estar subestimado.</t>
         </is>

--- a/docs/historico_fma.xlsx
+++ b/docs/historico_fma.xlsx
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em 15/10/2026 às 09:52 (Brasília). Uma aba por município.</t>
+          <t>Gerado em 15/10/2026 às 10:11 (Brasília). Uma aba por município.</t>
         </is>
       </c>
     </row>

--- a/docs/historico_fma.xlsx
+++ b/docs/historico_fma.xlsx
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em 15/10/2026 às 10:11 (Brasília). Uma aba por município.</t>
+          <t>Gerado em 15/10/2026 às 15:03 (Brasília). Uma aba por município.</t>
         </is>
       </c>
     </row>
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1768,6 +1768,26 @@
       </c>
       <c r="F59" t="inlineStr"/>
     </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D60" s="6" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1779,7 +1799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2984,6 +3004,26 @@
       </c>
       <c r="F59" t="inlineStr"/>
     </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D60" s="6" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2995,7 +3035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4200,6 +4240,26 @@
       </c>
       <c r="F59" t="inlineStr"/>
     </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D60" s="6" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4211,7 +4271,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5416,6 +5476,26 @@
       </c>
       <c r="F59" t="inlineStr"/>
     </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D60" s="6" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5427,7 +5507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6632,6 +6712,26 @@
       </c>
       <c r="F59" t="inlineStr"/>
     </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>86</v>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D60" s="6" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="E60" s="9" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6643,7 +6743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7848,6 +7948,26 @@
       </c>
       <c r="F59" t="inlineStr"/>
     </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>89</v>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D60" s="6" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7859,7 +7979,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9064,6 +9184,26 @@
       </c>
       <c r="F59" t="inlineStr"/>
     </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D60" s="6" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9075,7 +9215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10280,6 +10420,26 @@
       </c>
       <c r="F59" t="inlineStr"/>
     </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D60" s="6" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10291,7 +10451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11496,6 +11656,26 @@
       </c>
       <c r="F59" t="inlineStr"/>
     </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D60" s="6" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11507,7 +11687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12712,6 +12892,26 @@
       </c>
       <c r="F59" t="inlineStr"/>
     </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>89</v>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D60" s="6" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12723,7 +12923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13928,6 +14128,26 @@
       </c>
       <c r="F59" t="inlineStr"/>
     </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D60" s="6" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13939,7 +14159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14884,6 +15104,26 @@
       </c>
       <c r="F46" t="inlineStr"/>
     </row>
+    <row r="47">
+      <c r="A47" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D47" s="6" t="n">
+        <v>10.84</v>
+      </c>
+      <c r="E47" s="9" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14895,7 +15135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16100,6 +16340,26 @@
       </c>
       <c r="F59" t="inlineStr"/>
     </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D60" s="6" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16111,7 +16371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17316,6 +17576,26 @@
       </c>
       <c r="F59" t="inlineStr"/>
     </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D60" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17327,7 +17607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18532,6 +18812,26 @@
       </c>
       <c r="F59" t="inlineStr"/>
     </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D60" s="6" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/historico_fma.xlsx
+++ b/docs/historico_fma.xlsx
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em 15/10/2026 às 15:03 (Brasília). Uma aba por município.</t>
+          <t>Gerado em 15/10/2026 às 17:28 (Brasília). Uma aba por município.</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1776,7 @@
         <v>63</v>
       </c>
       <c r="C60" s="5" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="D60" s="6" t="n">
         <v>5.95</v>
@@ -3009,17 +3009,17 @@
         <v>46310</v>
       </c>
       <c r="B60" s="5" t="n">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="C60" s="5" t="n">
-        <v>5.5</v>
+        <v>2</v>
       </c>
       <c r="D60" s="6" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="E60" s="7" t="inlineStr">
-        <is>
-          <t>Pequeno</t>
+        <v>5.59</v>
+      </c>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
@@ -4245,17 +4245,17 @@
         <v>46310</v>
       </c>
       <c r="B60" s="5" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C60" s="5" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="D60" s="6" t="n">
-        <v>6.57</v>
-      </c>
-      <c r="E60" s="8" t="inlineStr">
-        <is>
-          <t>Médio</t>
+        <v>8.880000000000001</v>
+      </c>
+      <c r="E60" s="9" t="inlineStr">
+        <is>
+          <t>Alto</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
@@ -5481,17 +5481,17 @@
         <v>46310</v>
       </c>
       <c r="B60" s="5" t="n">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="C60" s="5" t="n">
-        <v>5.5</v>
+        <v>2</v>
       </c>
       <c r="D60" s="6" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="E60" s="7" t="inlineStr">
-        <is>
-          <t>Pequeno</t>
+        <v>5.59</v>
+      </c>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
@@ -6717,13 +6717,13 @@
         <v>46310</v>
       </c>
       <c r="B60" s="5" t="n">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="C60" s="5" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="D60" s="6" t="n">
-        <v>8.220000000000001</v>
+        <v>8.35</v>
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
@@ -7953,17 +7953,17 @@
         <v>46310</v>
       </c>
       <c r="B60" s="5" t="n">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="C60" s="5" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="D60" s="6" t="n">
-        <v>6.96</v>
-      </c>
-      <c r="E60" s="8" t="inlineStr">
-        <is>
-          <t>Médio</t>
+        <v>9.789999999999999</v>
+      </c>
+      <c r="E60" s="9" t="inlineStr">
+        <is>
+          <t>Alto</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
@@ -9189,13 +9189,13 @@
         <v>46310</v>
       </c>
       <c r="B60" s="5" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C60" s="5" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="D60" s="6" t="n">
-        <v>5.82</v>
+        <v>5.92</v>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
@@ -10425,13 +10425,13 @@
         <v>46310</v>
       </c>
       <c r="B60" s="5" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C60" s="5" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="D60" s="6" t="n">
-        <v>5.89</v>
+        <v>5.99</v>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
@@ -11664,7 +11664,7 @@
         <v>63</v>
       </c>
       <c r="C60" s="5" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="D60" s="6" t="n">
         <v>5.95</v>
@@ -12897,17 +12897,17 @@
         <v>46310</v>
       </c>
       <c r="B60" s="5" t="n">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="C60" s="5" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="D60" s="6" t="n">
-        <v>6.96</v>
-      </c>
-      <c r="E60" s="8" t="inlineStr">
-        <is>
-          <t>Médio</t>
+        <v>9.789999999999999</v>
+      </c>
+      <c r="E60" s="9" t="inlineStr">
+        <is>
+          <t>Alto</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
@@ -14133,17 +14133,17 @@
         <v>46310</v>
       </c>
       <c r="B60" s="5" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C60" s="5" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="D60" s="6" t="n">
-        <v>6.57</v>
-      </c>
-      <c r="E60" s="8" t="inlineStr">
-        <is>
-          <t>Médio</t>
+        <v>8.880000000000001</v>
+      </c>
+      <c r="E60" s="9" t="inlineStr">
+        <is>
+          <t>Alto</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
@@ -15109,13 +15109,13 @@
         <v>46310</v>
       </c>
       <c r="B47" s="5" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="D47" s="6" t="n">
-        <v>10.84</v>
+        <v>10.89</v>
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
@@ -16348,7 +16348,7 @@
         <v>63</v>
       </c>
       <c r="C60" s="5" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="D60" s="6" t="n">
         <v>5.95</v>
@@ -17584,7 +17584,7 @@
         <v>70</v>
       </c>
       <c r="C60" s="5" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="D60" s="6" t="n">
         <v>4.3</v>
@@ -18817,17 +18817,17 @@
         <v>46310</v>
       </c>
       <c r="B60" s="5" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C60" s="5" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="D60" s="6" t="n">
-        <v>6.57</v>
-      </c>
-      <c r="E60" s="8" t="inlineStr">
-        <is>
-          <t>Médio</t>
+        <v>8.880000000000001</v>
+      </c>
+      <c r="E60" s="9" t="inlineStr">
+        <is>
+          <t>Alto</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>

--- a/docs/historico_fma.xlsx
+++ b/docs/historico_fma.xlsx
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em 15/10/2026 às 17:28 (Brasília). Uma aba por município.</t>
+          <t>Gerado em 16/10/2026 às 15:03 (Brasília). Uma aba por município.</t>
         </is>
       </c>
     </row>
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1773,13 +1773,13 @@
         <v>46310</v>
       </c>
       <c r="B60" s="5" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C60" s="5" t="n">
         <v>0.8</v>
       </c>
       <c r="D60" s="6" t="n">
-        <v>5.95</v>
+        <v>6</v>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
@@ -1787,6 +1787,26 @@
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="D61" s="6" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1799,7 +1819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3009,13 +3029,13 @@
         <v>46310</v>
       </c>
       <c r="B60" s="5" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C60" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D60" s="6" t="n">
-        <v>5.59</v>
+        <v>5.62</v>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
@@ -3023,6 +3043,26 @@
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="D61" s="6" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="E61" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3035,7 +3075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4245,13 +4285,13 @@
         <v>46310</v>
       </c>
       <c r="B60" s="5" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C60" s="5" t="n">
         <v>1.8</v>
       </c>
       <c r="D60" s="6" t="n">
-        <v>8.880000000000001</v>
+        <v>8.91</v>
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
@@ -4259,6 +4299,26 @@
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="D61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4271,7 +4331,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5481,13 +5541,13 @@
         <v>46310</v>
       </c>
       <c r="B60" s="5" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C60" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D60" s="6" t="n">
-        <v>5.59</v>
+        <v>5.62</v>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
@@ -5495,6 +5555,26 @@
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="D61" s="6" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="E61" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5507,7 +5587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6732,6 +6812,26 @@
       </c>
       <c r="F60" t="inlineStr"/>
     </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>78</v>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="D61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6743,7 +6843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7968,6 +8068,26 @@
       </c>
       <c r="F60" t="inlineStr"/>
     </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="D61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7979,7 +8099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9189,13 +9309,13 @@
         <v>46310</v>
       </c>
       <c r="B60" s="5" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C60" s="5" t="n">
         <v>0.4</v>
       </c>
       <c r="D60" s="6" t="n">
-        <v>5.92</v>
+        <v>5.94</v>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
@@ -9203,6 +9323,26 @@
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="D61" s="6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="E61" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9215,7 +9355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10425,13 +10565,13 @@
         <v>46310</v>
       </c>
       <c r="B60" s="5" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C60" s="5" t="n">
         <v>0.9</v>
       </c>
       <c r="D60" s="6" t="n">
-        <v>5.99</v>
+        <v>6.02</v>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
@@ -10439,6 +10579,26 @@
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="D61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10451,7 +10611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11661,13 +11821,13 @@
         <v>46310</v>
       </c>
       <c r="B60" s="5" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C60" s="5" t="n">
         <v>0.8</v>
       </c>
       <c r="D60" s="6" t="n">
-        <v>5.95</v>
+        <v>6</v>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
@@ -11675,6 +11835,26 @@
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="D61" s="6" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11687,7 +11867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12912,6 +13092,26 @@
       </c>
       <c r="F60" t="inlineStr"/>
     </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="D61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12923,7 +13123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14133,13 +14333,13 @@
         <v>46310</v>
       </c>
       <c r="B60" s="5" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C60" s="5" t="n">
         <v>1.8</v>
       </c>
       <c r="D60" s="6" t="n">
-        <v>8.880000000000001</v>
+        <v>8.91</v>
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
@@ -14147,6 +14347,26 @@
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="D61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14159,7 +14379,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15109,13 +15329,13 @@
         <v>46310</v>
       </c>
       <c r="B47" s="5" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C47" s="5" t="n">
         <v>0.9</v>
       </c>
       <c r="D47" s="6" t="n">
-        <v>10.89</v>
+        <v>10.93</v>
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
@@ -15123,6 +15343,26 @@
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="D48" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15135,7 +15375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16345,13 +16585,13 @@
         <v>46310</v>
       </c>
       <c r="B60" s="5" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C60" s="5" t="n">
         <v>0.8</v>
       </c>
       <c r="D60" s="6" t="n">
-        <v>5.95</v>
+        <v>6</v>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
@@ -16359,6 +16599,26 @@
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="D61" s="6" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16371,7 +16631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17581,13 +17841,13 @@
         <v>46310</v>
       </c>
       <c r="B60" s="5" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C60" s="5" t="n">
         <v>3.2</v>
       </c>
       <c r="D60" s="6" t="n">
-        <v>4.3</v>
+        <v>4.34</v>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
@@ -17595,6 +17855,26 @@
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="D61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17607,7 +17887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18817,13 +19097,13 @@
         <v>46310</v>
       </c>
       <c r="B60" s="5" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C60" s="5" t="n">
         <v>1.8</v>
       </c>
       <c r="D60" s="6" t="n">
-        <v>8.880000000000001</v>
+        <v>8.91</v>
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
@@ -18831,6 +19111,26 @@
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="D61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/historico_fma.xlsx
+++ b/docs/historico_fma.xlsx
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em 16/10/2026 às 15:03 (Brasília). Uma aba por município.</t>
+          <t>Gerado em 16/10/2026 às 17:26 (Brasília). Uma aba por município.</t>
         </is>
       </c>
     </row>
@@ -1793,17 +1793,17 @@
         <v>46311</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C61" s="5" t="n">
-        <v>11.2</v>
+        <v>9.4</v>
       </c>
       <c r="D61" s="6" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
-          <t>Pequeno</t>
+        <v>3.96</v>
+      </c>
+      <c r="E61" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
@@ -3049,13 +3049,13 @@
         <v>46311</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="C61" s="5" t="n">
-        <v>9.4</v>
+        <v>9.9</v>
       </c>
       <c r="D61" s="6" t="n">
-        <v>3.64</v>
+        <v>4.06</v>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
@@ -4305,10 +4305,10 @@
         <v>46311</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="C61" s="5" t="n">
-        <v>33.4</v>
+        <v>31.8</v>
       </c>
       <c r="D61" s="6" t="n">
         <v>0</v>
@@ -5561,13 +5561,13 @@
         <v>46311</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="C61" s="5" t="n">
-        <v>9.4</v>
+        <v>9.9</v>
       </c>
       <c r="D61" s="6" t="n">
-        <v>3.64</v>
+        <v>4.06</v>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
@@ -6817,17 +6817,17 @@
         <v>46311</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C61" s="5" t="n">
-        <v>13.4</v>
+        <v>12.1</v>
       </c>
       <c r="D61" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" s="10" t="inlineStr">
-        <is>
-          <t>Nulo</t>
+        <v>3.1</v>
+      </c>
+      <c r="E61" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
@@ -8073,10 +8073,10 @@
         <v>46311</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C61" s="5" t="n">
-        <v>16.6</v>
+        <v>15.6</v>
       </c>
       <c r="D61" s="6" t="n">
         <v>0</v>
@@ -9332,7 +9332,7 @@
         <v>68</v>
       </c>
       <c r="C61" s="5" t="n">
-        <v>8.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="D61" s="6" t="n">
         <v>3.85</v>
@@ -10585,17 +10585,17 @@
         <v>46311</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C61" s="5" t="n">
-        <v>13.3</v>
+        <v>12.6</v>
       </c>
       <c r="D61" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" s="10" t="inlineStr">
-        <is>
-          <t>Nulo</t>
+        <v>2.87</v>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
@@ -11841,17 +11841,17 @@
         <v>46311</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C61" s="5" t="n">
-        <v>11.2</v>
+        <v>9.4</v>
       </c>
       <c r="D61" s="6" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
-          <t>Pequeno</t>
+        <v>3.96</v>
+      </c>
+      <c r="E61" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
@@ -13097,10 +13097,10 @@
         <v>46311</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C61" s="5" t="n">
-        <v>16.6</v>
+        <v>15.6</v>
       </c>
       <c r="D61" s="6" t="n">
         <v>0</v>
@@ -14353,10 +14353,10 @@
         <v>46311</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="C61" s="5" t="n">
-        <v>33.4</v>
+        <v>31.8</v>
       </c>
       <c r="D61" s="6" t="n">
         <v>0</v>
@@ -15349,10 +15349,10 @@
         <v>46311</v>
       </c>
       <c r="B48" s="5" t="n">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="C48" s="5" t="n">
-        <v>15.1</v>
+        <v>13.8</v>
       </c>
       <c r="D48" s="6" t="n">
         <v>0</v>
@@ -16605,17 +16605,17 @@
         <v>46311</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C61" s="5" t="n">
-        <v>11.2</v>
+        <v>9.4</v>
       </c>
       <c r="D61" s="6" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
-          <t>Pequeno</t>
+        <v>3.96</v>
+      </c>
+      <c r="E61" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
@@ -17861,10 +17861,10 @@
         <v>46311</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C61" s="5" t="n">
-        <v>24.2</v>
+        <v>20.7</v>
       </c>
       <c r="D61" s="6" t="n">
         <v>0</v>
@@ -19117,10 +19117,10 @@
         <v>46311</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="C61" s="5" t="n">
-        <v>33.4</v>
+        <v>31.8</v>
       </c>
       <c r="D61" s="6" t="n">
         <v>0</v>

--- a/docs/historico_fma.xlsx
+++ b/docs/historico_fma.xlsx
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em 16/10/2026 às 17:26 (Brasília). Uma aba por município.</t>
+          <t>Gerado em 17/10/2026 às 14:52 (Brasília). Uma aba por município.</t>
         </is>
       </c>
     </row>
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1793,13 +1793,13 @@
         <v>46311</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="C61" s="5" t="n">
         <v>9.4</v>
       </c>
       <c r="D61" s="6" t="n">
-        <v>3.96</v>
+        <v>3.79</v>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
@@ -1807,6 +1807,26 @@
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>87</v>
+      </c>
+      <c r="C62" s="5" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="D62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1819,7 +1839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3049,13 +3069,13 @@
         <v>46311</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C61" s="5" t="n">
         <v>9.9</v>
       </c>
       <c r="D61" s="6" t="n">
-        <v>4.06</v>
+        <v>3.94</v>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
@@ -3063,6 +3083,26 @@
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>81</v>
+      </c>
+      <c r="C62" s="5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D62" s="6" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3075,7 +3115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4305,7 +4345,7 @@
         <v>46311</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C61" s="5" t="n">
         <v>31.8</v>
@@ -4319,6 +4359,26 @@
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="C62" s="5" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="D62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4331,7 +4391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5561,13 +5621,13 @@
         <v>46311</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C61" s="5" t="n">
         <v>9.9</v>
       </c>
       <c r="D61" s="6" t="n">
-        <v>4.06</v>
+        <v>3.94</v>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
@@ -5575,6 +5635,26 @@
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>81</v>
+      </c>
+      <c r="C62" s="5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D62" s="6" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5587,7 +5667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6832,6 +6912,26 @@
       </c>
       <c r="F61" t="inlineStr"/>
     </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>84</v>
+      </c>
+      <c r="C62" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="D62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6843,7 +6943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8073,7 +8173,7 @@
         <v>46311</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="C61" s="5" t="n">
         <v>15.6</v>
@@ -8087,6 +8187,26 @@
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="C62" s="5" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="D62" s="6" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8099,7 +8219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9329,13 +9449,13 @@
         <v>46311</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C61" s="5" t="n">
         <v>9.9</v>
       </c>
       <c r="D61" s="6" t="n">
-        <v>3.85</v>
+        <v>3.81</v>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
@@ -9343,6 +9463,26 @@
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="C62" s="5" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="D62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9355,7 +9495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10585,13 +10725,13 @@
         <v>46311</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C61" s="5" t="n">
         <v>12.6</v>
       </c>
       <c r="D61" s="6" t="n">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
@@ -10599,6 +10739,26 @@
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>81</v>
+      </c>
+      <c r="C62" s="5" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="D62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10611,7 +10771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11841,13 +12001,13 @@
         <v>46311</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="C61" s="5" t="n">
         <v>9.4</v>
       </c>
       <c r="D61" s="6" t="n">
-        <v>3.96</v>
+        <v>3.79</v>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
@@ -11855,6 +12015,26 @@
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>87</v>
+      </c>
+      <c r="C62" s="5" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="D62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11867,7 +12047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13097,7 +13277,7 @@
         <v>46311</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="C61" s="5" t="n">
         <v>15.6</v>
@@ -13111,6 +13291,26 @@
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="C62" s="5" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="D62" s="6" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13123,7 +13323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14353,7 +14553,7 @@
         <v>46311</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C61" s="5" t="n">
         <v>31.8</v>
@@ -14367,6 +14567,26 @@
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="C62" s="5" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="D62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14379,7 +14599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15349,7 +15569,7 @@
         <v>46311</v>
       </c>
       <c r="B48" s="5" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C48" s="5" t="n">
         <v>13.8</v>
@@ -15363,6 +15583,26 @@
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="D49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15375,7 +15615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16605,13 +16845,13 @@
         <v>46311</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="C61" s="5" t="n">
         <v>9.4</v>
       </c>
       <c r="D61" s="6" t="n">
-        <v>3.96</v>
+        <v>3.79</v>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
@@ -16619,6 +16859,26 @@
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>87</v>
+      </c>
+      <c r="C62" s="5" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="D62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16631,7 +16891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17861,7 +18121,7 @@
         <v>46311</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="C61" s="5" t="n">
         <v>20.7</v>
@@ -17875,6 +18135,26 @@
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="C62" s="5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="D62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17887,7 +18167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19117,7 +19397,7 @@
         <v>46311</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C61" s="5" t="n">
         <v>31.8</v>
@@ -19131,6 +19411,26 @@
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="C62" s="5" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="D62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/historico_fma.xlsx
+++ b/docs/historico_fma.xlsx
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em 17/10/2026 às 14:52 (Brasília). Uma aba por município.</t>
+          <t>Gerado em 17/10/2026 às 17:19 (Brasília). Uma aba por município.</t>
         </is>
       </c>
     </row>

--- a/docs/historico_fma.xlsx
+++ b/docs/historico_fma.xlsx
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em 17/10/2026 às 17:19 (Brasília). Uma aba por município.</t>
+          <t>Gerado em 18/10/2026 às 14:57 (Brasília). Uma aba por município.</t>
         </is>
       </c>
     </row>
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1813,10 +1813,10 @@
         <v>46312</v>
       </c>
       <c r="B62" s="5" t="n">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="C62" s="5" t="n">
-        <v>19.3</v>
+        <v>15.3</v>
       </c>
       <c r="D62" s="6" t="n">
         <v>0</v>
@@ -1827,6 +1827,26 @@
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="C63" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D63" s="6" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1839,7 +1859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3089,20 +3109,40 @@
         <v>46312</v>
       </c>
       <c r="B62" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="C62" s="5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="D62" s="6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B63" s="5" t="n">
         <v>81</v>
       </c>
-      <c r="C62" s="5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="D62" s="6" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="E62" s="7" t="inlineStr">
-        <is>
-          <t>Pequeno</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
+      <c r="C63" s="5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D63" s="6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3115,7 +3155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4365,10 +4405,10 @@
         <v>46312</v>
       </c>
       <c r="B62" s="5" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C62" s="5" t="n">
-        <v>21.3</v>
+        <v>19.2</v>
       </c>
       <c r="D62" s="6" t="n">
         <v>0</v>
@@ -4379,6 +4419,26 @@
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="C63" s="5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D63" s="6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4391,7 +4451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5641,20 +5701,40 @@
         <v>46312</v>
       </c>
       <c r="B62" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="C62" s="5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="D62" s="6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B63" s="5" t="n">
         <v>81</v>
       </c>
-      <c r="C62" s="5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="D62" s="6" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="E62" s="7" t="inlineStr">
-        <is>
-          <t>Pequeno</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
+      <c r="C63" s="5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D63" s="6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5667,7 +5747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6917,10 +6997,10 @@
         <v>46312</v>
       </c>
       <c r="B62" s="5" t="n">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="C62" s="5" t="n">
-        <v>24</v>
+        <v>21.4</v>
       </c>
       <c r="D62" s="6" t="n">
         <v>0</v>
@@ -6931,6 +7011,26 @@
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>86</v>
+      </c>
+      <c r="C63" s="5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="D63" s="6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6943,7 +7043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8193,13 +8293,13 @@
         <v>46312</v>
       </c>
       <c r="B62" s="5" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C62" s="5" t="n">
-        <v>12.3</v>
+        <v>11.3</v>
       </c>
       <c r="D62" s="6" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
@@ -8207,6 +8307,26 @@
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>84</v>
+      </c>
+      <c r="C63" s="5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D63" s="6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8219,7 +8339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9469,20 +9589,40 @@
         <v>46312</v>
       </c>
       <c r="B62" s="5" t="n">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C62" s="5" t="n">
-        <v>16.6</v>
+        <v>7.5</v>
       </c>
       <c r="D62" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" s="10" t="inlineStr">
-        <is>
-          <t>Nulo</t>
+        <v>3.11</v>
+      </c>
+      <c r="E62" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="C63" s="5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D63" s="6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9495,7 +9635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10745,20 +10885,40 @@
         <v>46312</v>
       </c>
       <c r="B62" s="5" t="n">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="C62" s="5" t="n">
-        <v>18.4</v>
+        <v>9.6</v>
       </c>
       <c r="D62" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" s="10" t="inlineStr">
-        <is>
-          <t>Nulo</t>
+        <v>2.51</v>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="C63" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D63" s="6" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10771,7 +10931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12021,10 +12181,10 @@
         <v>46312</v>
       </c>
       <c r="B62" s="5" t="n">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="C62" s="5" t="n">
-        <v>19.3</v>
+        <v>15.3</v>
       </c>
       <c r="D62" s="6" t="n">
         <v>0</v>
@@ -12035,6 +12195,26 @@
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="C63" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D63" s="6" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12047,7 +12227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13297,13 +13477,13 @@
         <v>46312</v>
       </c>
       <c r="B62" s="5" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C62" s="5" t="n">
-        <v>12.3</v>
+        <v>11.3</v>
       </c>
       <c r="D62" s="6" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
@@ -13311,6 +13491,26 @@
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>84</v>
+      </c>
+      <c r="C63" s="5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D63" s="6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13323,7 +13523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14573,10 +14773,10 @@
         <v>46312</v>
       </c>
       <c r="B62" s="5" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C62" s="5" t="n">
-        <v>21.3</v>
+        <v>19.2</v>
       </c>
       <c r="D62" s="6" t="n">
         <v>0</v>
@@ -14587,6 +14787,26 @@
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="C63" s="5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D63" s="6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14599,7 +14819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15589,10 +15809,10 @@
         <v>46312</v>
       </c>
       <c r="B49" s="5" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="C49" s="5" t="n">
-        <v>20.3</v>
+        <v>14.8</v>
       </c>
       <c r="D49" s="6" t="n">
         <v>0</v>
@@ -15603,6 +15823,26 @@
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>86</v>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="D50" s="6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15615,7 +15855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16865,10 +17105,10 @@
         <v>46312</v>
       </c>
       <c r="B62" s="5" t="n">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="C62" s="5" t="n">
-        <v>19.3</v>
+        <v>15.3</v>
       </c>
       <c r="D62" s="6" t="n">
         <v>0</v>
@@ -16879,6 +17119,26 @@
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="C63" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D63" s="6" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16891,7 +17151,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18141,20 +18401,40 @@
         <v>46312</v>
       </c>
       <c r="B62" s="5" t="n">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="C62" s="5" t="n">
-        <v>14.5</v>
+        <v>10.8</v>
       </c>
       <c r="D62" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" s="10" t="inlineStr">
-        <is>
-          <t>Nulo</t>
+        <v>1.41</v>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="C63" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D63" s="6" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18167,7 +18447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19417,10 +19697,10 @@
         <v>46312</v>
       </c>
       <c r="B62" s="5" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C62" s="5" t="n">
-        <v>21.3</v>
+        <v>19.2</v>
       </c>
       <c r="D62" s="6" t="n">
         <v>0</v>
@@ -19431,6 +19711,26 @@
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="C63" s="5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D63" s="6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/historico_fma.xlsx
+++ b/docs/historico_fma.xlsx
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em 18/10/2026 às 14:57 (Brasília). Uma aba por município.</t>
+          <t>Gerado em 18/10/2026 às 17:16 (Brasília). Uma aba por município.</t>
         </is>
       </c>
     </row>
@@ -1833,13 +1833,13 @@
         <v>46313</v>
       </c>
       <c r="B63" s="5" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C63" s="5" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="D63" s="6" t="n">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
@@ -3129,13 +3129,13 @@
         <v>46313</v>
       </c>
       <c r="B63" s="5" t="n">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="C63" s="5" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="D63" s="6" t="n">
-        <v>3.25</v>
+        <v>3.46</v>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
@@ -4425,13 +4425,13 @@
         <v>46313</v>
       </c>
       <c r="B63" s="5" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="D63" s="6" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
@@ -5721,13 +5721,13 @@
         <v>46313</v>
       </c>
       <c r="B63" s="5" t="n">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="C63" s="5" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="D63" s="6" t="n">
-        <v>3.25</v>
+        <v>3.46</v>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
@@ -7017,13 +7017,13 @@
         <v>46313</v>
       </c>
       <c r="B63" s="5" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4.7</v>
+        <v>2.9</v>
       </c>
       <c r="D63" s="6" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
@@ -8313,13 +8313,13 @@
         <v>46313</v>
       </c>
       <c r="B63" s="5" t="n">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="D63" s="6" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
@@ -9609,13 +9609,13 @@
         <v>46313</v>
       </c>
       <c r="B63" s="5" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C63" s="5" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="D63" s="6" t="n">
-        <v>4.6</v>
+        <v>4.67</v>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
@@ -10905,13 +10905,13 @@
         <v>46313</v>
       </c>
       <c r="B63" s="5" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C63" s="5" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="D63" s="6" t="n">
-        <v>3.34</v>
+        <v>3.48</v>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
@@ -12201,13 +12201,13 @@
         <v>46313</v>
       </c>
       <c r="B63" s="5" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C63" s="5" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="D63" s="6" t="n">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
@@ -13497,13 +13497,13 @@
         <v>46313</v>
       </c>
       <c r="B63" s="5" t="n">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="D63" s="6" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
@@ -14793,13 +14793,13 @@
         <v>46313</v>
       </c>
       <c r="B63" s="5" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="D63" s="6" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
@@ -15829,13 +15829,13 @@
         <v>46313</v>
       </c>
       <c r="B50" s="5" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C50" s="5" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="D50" s="6" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
@@ -17125,13 +17125,13 @@
         <v>46313</v>
       </c>
       <c r="B63" s="5" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C63" s="5" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="D63" s="6" t="n">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
@@ -18421,13 +18421,13 @@
         <v>46313</v>
       </c>
       <c r="B63" s="5" t="n">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C63" s="5" t="n">
         <v>3.5</v>
       </c>
       <c r="D63" s="6" t="n">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
@@ -19717,13 +19717,13 @@
         <v>46313</v>
       </c>
       <c r="B63" s="5" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="D63" s="6" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>

--- a/docs/historico_fma.xlsx
+++ b/docs/historico_fma.xlsx
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em 18/10/2026 às 17:16 (Brasília). Uma aba por município.</t>
+          <t>Gerado em 19/10/2026 às 15:01 (Brasília). Uma aba por município.</t>
         </is>
       </c>
     </row>
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1833,13 +1833,13 @@
         <v>46313</v>
       </c>
       <c r="B63" s="5" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C63" s="5" t="n">
         <v>1.4</v>
       </c>
       <c r="D63" s="6" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
@@ -1847,6 +1847,26 @@
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="C64" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D64" s="6" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1859,7 +1879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3129,13 +3149,13 @@
         <v>46313</v>
       </c>
       <c r="B63" s="5" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C63" s="5" t="n">
         <v>2.6</v>
       </c>
       <c r="D63" s="6" t="n">
-        <v>3.46</v>
+        <v>3.51</v>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
@@ -3143,6 +3163,26 @@
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="C64" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D64" s="6" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3155,7 +3195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4425,13 +4465,13 @@
         <v>46313</v>
       </c>
       <c r="B63" s="5" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C63" s="5" t="n">
         <v>3.8</v>
       </c>
       <c r="D63" s="6" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
@@ -4439,6 +4479,26 @@
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="C64" s="5" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="D64" s="6" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4451,7 +4511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5721,13 +5781,13 @@
         <v>46313</v>
       </c>
       <c r="B63" s="5" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C63" s="5" t="n">
         <v>2.6</v>
       </c>
       <c r="D63" s="6" t="n">
-        <v>3.46</v>
+        <v>3.51</v>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
@@ -5735,6 +5795,26 @@
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="C64" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D64" s="6" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5747,7 +5827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7032,6 +7112,26 @@
       </c>
       <c r="F63" t="inlineStr"/>
     </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="C64" s="5" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="D64" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7043,7 +7143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8328,6 +8428,26 @@
       </c>
       <c r="F63" t="inlineStr"/>
     </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="C64" s="5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D64" s="6" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8339,7 +8459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9624,6 +9744,26 @@
       </c>
       <c r="F63" t="inlineStr"/>
     </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="C64" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D64" s="6" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9635,7 +9775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10905,13 +11045,13 @@
         <v>46313</v>
       </c>
       <c r="B63" s="5" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C63" s="5" t="n">
         <v>3.2</v>
       </c>
       <c r="D63" s="6" t="n">
-        <v>3.48</v>
+        <v>3.51</v>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
@@ -10919,6 +11059,26 @@
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="C64" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D64" s="6" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10931,7 +11091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12201,13 +12361,13 @@
         <v>46313</v>
       </c>
       <c r="B63" s="5" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C63" s="5" t="n">
         <v>1.4</v>
       </c>
       <c r="D63" s="6" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
@@ -12215,6 +12375,26 @@
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="C64" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D64" s="6" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12227,7 +12407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13512,6 +13692,26 @@
       </c>
       <c r="F63" t="inlineStr"/>
     </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="C64" s="5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D64" s="6" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13523,7 +13723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14793,13 +14993,13 @@
         <v>46313</v>
       </c>
       <c r="B63" s="5" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C63" s="5" t="n">
         <v>3.8</v>
       </c>
       <c r="D63" s="6" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
@@ -14807,6 +15007,26 @@
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="C64" s="5" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="D64" s="6" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14819,7 +15039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15829,13 +16049,13 @@
         <v>46313</v>
       </c>
       <c r="B50" s="5" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C50" s="5" t="n">
         <v>3.5</v>
       </c>
       <c r="D50" s="6" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
@@ -15843,6 +16063,26 @@
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>82</v>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="D51" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15855,7 +16095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17125,13 +17365,13 @@
         <v>46313</v>
       </c>
       <c r="B63" s="5" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C63" s="5" t="n">
         <v>1.4</v>
       </c>
       <c r="D63" s="6" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
@@ -17139,6 +17379,26 @@
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="C64" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D64" s="6" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17151,7 +17411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18421,13 +18681,13 @@
         <v>46313</v>
       </c>
       <c r="B63" s="5" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C63" s="5" t="n">
         <v>3.5</v>
       </c>
       <c r="D63" s="6" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
@@ -18435,6 +18695,26 @@
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="C64" s="5" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="D64" s="6" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18447,7 +18727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19717,13 +19997,13 @@
         <v>46313</v>
       </c>
       <c r="B63" s="5" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C63" s="5" t="n">
         <v>3.8</v>
       </c>
       <c r="D63" s="6" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
@@ -19731,6 +20011,26 @@
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="C64" s="5" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="D64" s="6" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/historico_fma.xlsx
+++ b/docs/historico_fma.xlsx
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em 19/10/2026 às 15:01 (Brasília). Uma aba por município.</t>
+          <t>Gerado em 19/10/2026 às 17:29 (Brasília). Uma aba por município.</t>
         </is>
       </c>
     </row>
@@ -1853,13 +1853,13 @@
         <v>46314</v>
       </c>
       <c r="B64" s="5" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C64" s="5" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="D64" s="6" t="n">
-        <v>2.98</v>
+        <v>2.46</v>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
@@ -4485,13 +4485,13 @@
         <v>46314</v>
       </c>
       <c r="B64" s="5" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="C64" s="5" t="n">
-        <v>9.699999999999999</v>
+        <v>11.7</v>
       </c>
       <c r="D64" s="6" t="n">
-        <v>2.23</v>
+        <v>1.72</v>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
@@ -7117,10 +7117,10 @@
         <v>46314</v>
       </c>
       <c r="B64" s="5" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="C64" s="5" t="n">
-        <v>18.3</v>
+        <v>18.6</v>
       </c>
       <c r="D64" s="6" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
         <v>62</v>
       </c>
       <c r="C64" s="5" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="D64" s="6" t="n">
         <v>3.57</v>
@@ -9749,13 +9749,13 @@
         <v>46314</v>
       </c>
       <c r="B64" s="5" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C64" s="5" t="n">
         <v>0.2</v>
       </c>
       <c r="D64" s="6" t="n">
-        <v>6.21</v>
+        <v>6.19</v>
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
@@ -11068,10 +11068,10 @@
         <v>69</v>
       </c>
       <c r="C64" s="5" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="D64" s="6" t="n">
-        <v>3.91</v>
+        <v>4.96</v>
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
@@ -12381,13 +12381,13 @@
         <v>46314</v>
       </c>
       <c r="B64" s="5" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C64" s="5" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="D64" s="6" t="n">
-        <v>2.98</v>
+        <v>2.46</v>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
@@ -13700,7 +13700,7 @@
         <v>62</v>
       </c>
       <c r="C64" s="5" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="D64" s="6" t="n">
         <v>3.57</v>
@@ -15013,13 +15013,13 @@
         <v>46314</v>
       </c>
       <c r="B64" s="5" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="C64" s="5" t="n">
-        <v>9.699999999999999</v>
+        <v>11.7</v>
       </c>
       <c r="D64" s="6" t="n">
-        <v>2.23</v>
+        <v>1.72</v>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
@@ -16069,10 +16069,10 @@
         <v>46314</v>
       </c>
       <c r="B51" s="5" t="n">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C51" s="5" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="D51" s="6" t="n">
         <v>0</v>
@@ -17385,13 +17385,13 @@
         <v>46314</v>
       </c>
       <c r="B64" s="5" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C64" s="5" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="D64" s="6" t="n">
-        <v>2.98</v>
+        <v>2.46</v>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
@@ -18701,13 +18701,13 @@
         <v>46314</v>
       </c>
       <c r="B64" s="5" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="C64" s="5" t="n">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="D64" s="6" t="n">
-        <v>2.36</v>
+        <v>2.23</v>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
@@ -20017,13 +20017,13 @@
         <v>46314</v>
       </c>
       <c r="B64" s="5" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="C64" s="5" t="n">
-        <v>9.699999999999999</v>
+        <v>11.7</v>
       </c>
       <c r="D64" s="6" t="n">
-        <v>2.23</v>
+        <v>1.72</v>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>

--- a/docs/historico_fma.xlsx
+++ b/docs/historico_fma.xlsx
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em 19/10/2026 às 17:29 (Brasília). Uma aba por município.</t>
+          <t>Gerado em 20/10/2026 às 15:05 (Brasília). Uma aba por município.</t>
         </is>
       </c>
     </row>
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1868,6 +1868,26 @@
       </c>
       <c r="F64" t="inlineStr"/>
     </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B65" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="C65" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D65" s="6" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1879,7 +1899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3184,6 +3204,26 @@
       </c>
       <c r="F64" t="inlineStr"/>
     </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B65" s="5" t="n">
+        <v>78</v>
+      </c>
+      <c r="C65" s="5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="D65" s="6" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3195,7 +3235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4500,6 +4540,26 @@
       </c>
       <c r="F64" t="inlineStr"/>
     </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B65" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="C65" s="5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D65" s="6" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4511,7 +4571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5816,6 +5876,26 @@
       </c>
       <c r="F64" t="inlineStr"/>
     </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B65" s="5" t="n">
+        <v>78</v>
+      </c>
+      <c r="C65" s="5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="D65" s="6" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5827,7 +5907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7117,7 +7197,7 @@
         <v>46314</v>
       </c>
       <c r="B64" s="5" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C64" s="5" t="n">
         <v>18.6</v>
@@ -7131,6 +7211,26 @@
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B65" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="C65" s="5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="D65" s="6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7143,7 +7243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8433,13 +8533,13 @@
         <v>46314</v>
       </c>
       <c r="B64" s="5" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C64" s="5" t="n">
         <v>4.9</v>
       </c>
       <c r="D64" s="6" t="n">
-        <v>3.57</v>
+        <v>3.55</v>
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
@@ -8447,6 +8547,26 @@
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B65" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="C65" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D65" s="6" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8459,7 +8579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9749,13 +9869,13 @@
         <v>46314</v>
       </c>
       <c r="B64" s="5" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C64" s="5" t="n">
         <v>0.2</v>
       </c>
       <c r="D64" s="6" t="n">
-        <v>6.19</v>
+        <v>6.16</v>
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
@@ -9763,6 +9883,26 @@
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B65" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="C65" s="5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D65" s="6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9775,7 +9915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11080,6 +11220,26 @@
       </c>
       <c r="F64" t="inlineStr"/>
     </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B65" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="C65" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D65" s="6" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11091,7 +11251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12396,6 +12556,26 @@
       </c>
       <c r="F64" t="inlineStr"/>
     </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B65" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="C65" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D65" s="6" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12407,7 +12587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13697,13 +13877,13 @@
         <v>46314</v>
       </c>
       <c r="B64" s="5" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C64" s="5" t="n">
         <v>4.9</v>
       </c>
       <c r="D64" s="6" t="n">
-        <v>3.57</v>
+        <v>3.55</v>
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
@@ -13711,6 +13891,26 @@
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B65" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="C65" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D65" s="6" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13723,7 +13923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15028,6 +15228,26 @@
       </c>
       <c r="F64" t="inlineStr"/>
     </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B65" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="C65" s="5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D65" s="6" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15039,7 +15259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16084,6 +16304,26 @@
       </c>
       <c r="F51" t="inlineStr"/>
     </row>
+    <row r="52">
+      <c r="A52" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>81</v>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D52" s="6" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16095,7 +16335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17400,6 +17640,26 @@
       </c>
       <c r="F64" t="inlineStr"/>
     </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B65" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="C65" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D65" s="6" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17411,7 +17671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18701,13 +18961,13 @@
         <v>46314</v>
       </c>
       <c r="B64" s="5" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C64" s="5" t="n">
         <v>6.5</v>
       </c>
       <c r="D64" s="6" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
@@ -18715,6 +18975,26 @@
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B65" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="C65" s="5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D65" s="6" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18727,7 +19007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20032,6 +20312,26 @@
       </c>
       <c r="F64" t="inlineStr"/>
     </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B65" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="C65" s="5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D65" s="6" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/historico_fma.xlsx
+++ b/docs/historico_fma.xlsx
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em 20/10/2026 às 15:05 (Brasília). Uma aba por município.</t>
+          <t>Gerado em 20/10/2026 às 17:26 (Brasília). Uma aba por município.</t>
         </is>
       </c>
     </row>

--- a/docs/historico_fma.xlsx
+++ b/docs/historico_fma.xlsx
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em 20/10/2026 às 17:26 (Brasília). Uma aba por município.</t>
+          <t>Gerado em 21/10/2026 às 15:02 (Brasília). Uma aba por município.</t>
         </is>
       </c>
     </row>
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1873,13 +1873,13 @@
         <v>46315</v>
       </c>
       <c r="B65" s="5" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="D65" s="6" t="n">
-        <v>3.89</v>
+        <v>3.85</v>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
@@ -1887,6 +1887,26 @@
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="C66" s="5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="D66" s="6" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1899,7 +1919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3209,13 +3229,13 @@
         <v>46315</v>
       </c>
       <c r="B65" s="5" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="D65" s="6" t="n">
-        <v>5.16</v>
+        <v>5.07</v>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
@@ -3223,6 +3243,26 @@
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="C66" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" s="6" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3235,7 +3275,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4545,13 +4585,13 @@
         <v>46315</v>
       </c>
       <c r="B65" s="5" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C65" s="5" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="D65" s="6" t="n">
-        <v>2.67</v>
+        <v>2.52</v>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
@@ -4559,6 +4599,26 @@
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="C66" s="5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D66" s="6" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4571,7 +4631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5881,13 +5941,13 @@
         <v>46315</v>
       </c>
       <c r="B65" s="5" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="D65" s="6" t="n">
-        <v>5.16</v>
+        <v>5.07</v>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
@@ -5895,6 +5955,26 @@
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="C66" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" s="6" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5907,7 +5987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7217,13 +7297,13 @@
         <v>46315</v>
       </c>
       <c r="B65" s="5" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C65" s="5" t="n">
-        <v>9.6</v>
+        <v>8.1</v>
       </c>
       <c r="D65" s="6" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
@@ -7231,6 +7311,26 @@
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="C66" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D66" s="6" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7243,7 +7343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8553,20 +8653,40 @@
         <v>46315</v>
       </c>
       <c r="B65" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="C65" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D65" s="6" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B66" s="5" t="n">
         <v>68</v>
       </c>
-      <c r="C65" s="5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="D65" s="6" t="n">
-        <v>5.02</v>
-      </c>
-      <c r="E65" s="8" t="inlineStr">
-        <is>
-          <t>Médio</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr"/>
+      <c r="C66" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D66" s="6" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8579,7 +8699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9892,7 +10012,7 @@
         <v>61</v>
       </c>
       <c r="C65" s="5" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D65" s="6" t="n">
         <v>7.8</v>
@@ -9903,6 +10023,26 @@
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="C66" s="5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D66" s="6" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9915,7 +10055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11225,13 +11365,13 @@
         <v>46315</v>
       </c>
       <c r="B65" s="5" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C65" s="5" t="n">
         <v>0.1</v>
       </c>
       <c r="D65" s="6" t="n">
-        <v>6.47</v>
+        <v>6.37</v>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
@@ -11239,6 +11379,26 @@
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="C66" s="5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D66" s="6" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11251,7 +11411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12561,13 +12721,13 @@
         <v>46315</v>
       </c>
       <c r="B65" s="5" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="D65" s="6" t="n">
-        <v>3.89</v>
+        <v>3.85</v>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
@@ -12575,6 +12735,26 @@
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="C66" s="5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="D66" s="6" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12587,7 +12767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13897,20 +14077,40 @@
         <v>46315</v>
       </c>
       <c r="B65" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="C65" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D65" s="6" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B66" s="5" t="n">
         <v>68</v>
       </c>
-      <c r="C65" s="5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="D65" s="6" t="n">
-        <v>5.02</v>
-      </c>
-      <c r="E65" s="8" t="inlineStr">
-        <is>
-          <t>Médio</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr"/>
+      <c r="C66" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D66" s="6" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13923,7 +14123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15233,13 +15433,13 @@
         <v>46315</v>
       </c>
       <c r="B65" s="5" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C65" s="5" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="D65" s="6" t="n">
-        <v>2.67</v>
+        <v>2.52</v>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
@@ -15247,6 +15447,26 @@
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="C66" s="5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D66" s="6" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15259,7 +15479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16309,13 +16529,13 @@
         <v>46315</v>
       </c>
       <c r="B52" s="5" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C52" s="5" t="n">
         <v>3.5</v>
       </c>
       <c r="D52" s="6" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
@@ -16323,6 +16543,26 @@
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D53" s="6" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16335,7 +16575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17645,13 +17885,13 @@
         <v>46315</v>
       </c>
       <c r="B65" s="5" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="D65" s="6" t="n">
-        <v>3.89</v>
+        <v>3.85</v>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
@@ -17659,6 +17899,26 @@
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="C66" s="5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="D66" s="6" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17671,7 +17931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18984,7 +19244,7 @@
         <v>71</v>
       </c>
       <c r="C65" s="5" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="D65" s="6" t="n">
         <v>2.96</v>
@@ -18995,6 +19255,26 @@
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="C66" s="5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D66" s="6" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -19007,7 +19287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20317,13 +20597,13 @@
         <v>46315</v>
       </c>
       <c r="B65" s="5" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C65" s="5" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="D65" s="6" t="n">
-        <v>2.67</v>
+        <v>2.52</v>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
@@ -20331,6 +20611,26 @@
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="C66" s="5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D66" s="6" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/historico_fma.xlsx
+++ b/docs/historico_fma.xlsx
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em 21/10/2026 às 15:02 (Brasília). Uma aba por município.</t>
+          <t>Gerado em 21/10/2026 às 17:27 (Brasília). Uma aba por município.</t>
         </is>
       </c>
     </row>

--- a/docs/historico_fma.xlsx
+++ b/docs/historico_fma.xlsx
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em 21/10/2026 às 17:27 (Brasília). Uma aba por município.</t>
+          <t>Gerado em 22/10/2026 às 15:02 (Brasília). Uma aba por município.</t>
         </is>
       </c>
     </row>
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1893,13 +1893,13 @@
         <v>46316</v>
       </c>
       <c r="B66" s="5" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C66" s="5" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="D66" s="6" t="n">
-        <v>5.15</v>
+        <v>3.98</v>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
@@ -1907,6 +1907,26 @@
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="C67" s="5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D67" s="6" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1919,7 +1939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3249,13 +3269,13 @@
         <v>46316</v>
       </c>
       <c r="B66" s="5" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C66" s="5" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="D66" s="6" t="n">
-        <v>6.41</v>
+        <v>6.42</v>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
@@ -3263,6 +3283,26 @@
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="C67" s="5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="D67" s="6" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3275,7 +3315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4605,13 +4645,13 @@
         <v>46316</v>
       </c>
       <c r="B66" s="5" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C66" s="5" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="D66" s="6" t="n">
-        <v>3.93</v>
+        <v>3.87</v>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
@@ -4619,6 +4659,26 @@
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="C67" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D67" s="6" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4631,7 +4691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5961,13 +6021,13 @@
         <v>46316</v>
       </c>
       <c r="B66" s="5" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C66" s="5" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="D66" s="6" t="n">
-        <v>6.41</v>
+        <v>6.42</v>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
@@ -5975,6 +6035,26 @@
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="C67" s="5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="D67" s="6" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5987,7 +6067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7317,13 +7397,13 @@
         <v>46316</v>
       </c>
       <c r="B66" s="5" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C66" s="5" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D66" s="6" t="n">
-        <v>2.84</v>
+        <v>2.72</v>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
@@ -7331,6 +7411,26 @@
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="C67" s="5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="D67" s="6" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7343,7 +7443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8673,13 +8773,13 @@
         <v>46316</v>
       </c>
       <c r="B66" s="5" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C66" s="5" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="D66" s="6" t="n">
-        <v>6.41</v>
+        <v>6.31</v>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
@@ -8687,6 +8787,26 @@
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="C67" s="5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="D67" s="6" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8699,7 +8819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10029,13 +10149,13 @@
         <v>46316</v>
       </c>
       <c r="B66" s="5" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C66" s="5" t="n">
         <v>3.8</v>
       </c>
       <c r="D66" s="6" t="n">
-        <v>6.89</v>
+        <v>6.85</v>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
@@ -10043,6 +10163,26 @@
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="C67" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D67" s="6" t="n">
+        <v>8.34</v>
+      </c>
+      <c r="E67" s="9" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10055,7 +10195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11385,20 +11525,40 @@
         <v>46316</v>
       </c>
       <c r="B66" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="C66" s="5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D66" s="6" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B67" s="5" t="n">
         <v>71</v>
       </c>
-      <c r="C66" s="5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D66" s="6" t="n">
-        <v>7.78</v>
-      </c>
-      <c r="E66" s="8" t="inlineStr">
-        <is>
-          <t>Médio</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr"/>
+      <c r="C67" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D67" s="6" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="E67" s="9" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11411,7 +11571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12741,13 +12901,13 @@
         <v>46316</v>
       </c>
       <c r="B66" s="5" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C66" s="5" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="D66" s="6" t="n">
-        <v>5.15</v>
+        <v>3.98</v>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
@@ -12755,6 +12915,26 @@
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="C67" s="5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D67" s="6" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12767,7 +12947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14097,13 +14277,13 @@
         <v>46316</v>
       </c>
       <c r="B66" s="5" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C66" s="5" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="D66" s="6" t="n">
-        <v>6.41</v>
+        <v>6.31</v>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
@@ -14111,6 +14291,26 @@
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="C67" s="5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="D67" s="6" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14123,7 +14323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15453,13 +15653,13 @@
         <v>46316</v>
       </c>
       <c r="B66" s="5" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C66" s="5" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="D66" s="6" t="n">
-        <v>3.93</v>
+        <v>3.87</v>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
@@ -15467,6 +15667,26 @@
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="C67" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D67" s="6" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15479,7 +15699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16549,13 +16769,13 @@
         <v>46316</v>
       </c>
       <c r="B53" s="5" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C53" s="5" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="D53" s="6" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
@@ -16563,6 +16783,26 @@
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>82</v>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="D54" s="6" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16575,7 +16815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17905,13 +18145,13 @@
         <v>46316</v>
       </c>
       <c r="B66" s="5" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C66" s="5" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="D66" s="6" t="n">
-        <v>5.15</v>
+        <v>3.98</v>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
@@ -17919,6 +18159,26 @@
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="C67" s="5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D67" s="6" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17931,7 +18191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19261,20 +19521,40 @@
         <v>46316</v>
       </c>
       <c r="B66" s="5" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C66" s="5" t="n">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="D66" s="6" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="E66" s="8" t="inlineStr">
-        <is>
-          <t>Médio</t>
+        <v>2.37</v>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="C67" s="5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="D67" s="6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -19287,7 +19567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20617,13 +20897,13 @@
         <v>46316</v>
       </c>
       <c r="B66" s="5" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C66" s="5" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="D66" s="6" t="n">
-        <v>3.93</v>
+        <v>3.87</v>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
@@ -20631,6 +20911,26 @@
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="C67" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D67" s="6" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/historico_fma.xlsx
+++ b/docs/historico_fma.xlsx
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em 22/10/2026 às 15:02 (Brasília). Uma aba por município.</t>
+          <t>Gerado em 22/10/2026 às 17:28 (Brasília). Uma aba por município.</t>
         </is>
       </c>
     </row>

--- a/docs/historico_fma.xlsx
+++ b/docs/historico_fma.xlsx
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em 22/10/2026 às 17:28 (Brasília). Uma aba por município.</t>
+          <t>Gerado em 23/10/2026 às 15:02 (Brasília). Uma aba por município.</t>
         </is>
       </c>
     </row>
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1916,7 +1916,7 @@
         <v>71</v>
       </c>
       <c r="C67" s="5" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="D67" s="6" t="n">
         <v>4.19</v>
@@ -1927,6 +1927,26 @@
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="C68" s="5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D68" s="6" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1939,7 +1959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3289,13 +3309,13 @@
         <v>46317</v>
       </c>
       <c r="B67" s="5" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C67" s="5" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="D67" s="6" t="n">
-        <v>3.82</v>
+        <v>3.85</v>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
@@ -3303,6 +3323,26 @@
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>81</v>
+      </c>
+      <c r="C68" s="5" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="D68" s="6" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3315,7 +3355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4665,13 +4705,13 @@
         <v>46317</v>
       </c>
       <c r="B67" s="5" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="C67" s="5" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="D67" s="6" t="n">
-        <v>5.26</v>
+        <v>5.1</v>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
@@ -4679,6 +4719,26 @@
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>79</v>
+      </c>
+      <c r="C68" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D68" s="6" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4691,7 +4751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6041,13 +6101,13 @@
         <v>46317</v>
       </c>
       <c r="B67" s="5" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C67" s="5" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="D67" s="6" t="n">
-        <v>3.82</v>
+        <v>3.85</v>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
@@ -6055,6 +6115,26 @@
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>81</v>
+      </c>
+      <c r="C68" s="5" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="D68" s="6" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6067,7 +6147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7417,13 +7497,13 @@
         <v>46317</v>
       </c>
       <c r="B67" s="5" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C67" s="5" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="D67" s="6" t="n">
-        <v>3.16</v>
+        <v>3.13</v>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
@@ -7431,6 +7511,26 @@
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="C68" s="5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D68" s="6" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7443,7 +7543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8793,20 +8893,40 @@
         <v>46317</v>
       </c>
       <c r="B67" s="5" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C67" s="5" t="n">
-        <v>5.7</v>
+        <v>6.3</v>
       </c>
       <c r="D67" s="6" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>78</v>
+      </c>
+      <c r="C68" s="5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D68" s="6" t="n">
         <v>3.97</v>
       </c>
-      <c r="E67" s="8" t="inlineStr">
-        <is>
-          <t>Médio</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr"/>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8819,7 +8939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10169,20 +10289,40 @@
         <v>46317</v>
       </c>
       <c r="B67" s="5" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C67" s="5" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="D67" s="6" t="n">
-        <v>8.34</v>
-      </c>
-      <c r="E67" s="9" t="inlineStr">
-        <is>
-          <t>Alto</t>
+        <v>6.15</v>
+      </c>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="C68" s="5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="D68" s="6" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10195,7 +10335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11545,13 +11685,13 @@
         <v>46317</v>
       </c>
       <c r="B67" s="5" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C67" s="5" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="D67" s="6" t="n">
-        <v>9.16</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="E67" s="9" t="inlineStr">
         <is>
@@ -11559,6 +11699,26 @@
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="C68" s="5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="D68" s="6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11571,7 +11731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12924,7 +13084,7 @@
         <v>71</v>
       </c>
       <c r="C67" s="5" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="D67" s="6" t="n">
         <v>4.19</v>
@@ -12935,6 +13095,26 @@
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="C68" s="5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D68" s="6" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12947,7 +13127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14297,20 +14477,40 @@
         <v>46317</v>
       </c>
       <c r="B67" s="5" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C67" s="5" t="n">
-        <v>5.7</v>
+        <v>6.3</v>
       </c>
       <c r="D67" s="6" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>78</v>
+      </c>
+      <c r="C68" s="5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D68" s="6" t="n">
         <v>3.97</v>
       </c>
-      <c r="E67" s="8" t="inlineStr">
-        <is>
-          <t>Médio</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr"/>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14323,7 +14523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15673,13 +15873,13 @@
         <v>46317</v>
       </c>
       <c r="B67" s="5" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="C67" s="5" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="D67" s="6" t="n">
-        <v>5.26</v>
+        <v>5.1</v>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
@@ -15687,6 +15887,26 @@
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>79</v>
+      </c>
+      <c r="C68" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D68" s="6" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15699,7 +15919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16789,13 +17009,13 @@
         <v>46317</v>
       </c>
       <c r="B54" s="5" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C54" s="5" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="D54" s="6" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
@@ -16803,6 +17023,26 @@
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="D55" s="6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16815,7 +17055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18168,7 +18408,7 @@
         <v>71</v>
       </c>
       <c r="C67" s="5" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="D67" s="6" t="n">
         <v>4.19</v>
@@ -18179,6 +18419,26 @@
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="C68" s="5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D68" s="6" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18191,7 +18451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19541,20 +19801,40 @@
         <v>46317</v>
       </c>
       <c r="B67" s="5" t="n">
+        <v>82</v>
+      </c>
+      <c r="C67" s="5" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="D67" s="6" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B68" s="5" t="n">
         <v>77</v>
       </c>
-      <c r="C67" s="5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="D67" s="6" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="E67" s="7" t="inlineStr">
-        <is>
-          <t>Pequeno</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr"/>
+      <c r="C68" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D68" s="6" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -19567,7 +19847,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20917,13 +21197,13 @@
         <v>46317</v>
       </c>
       <c r="B67" s="5" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="C67" s="5" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="D67" s="6" t="n">
-        <v>5.26</v>
+        <v>5.1</v>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
@@ -20931,6 +21211,26 @@
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>79</v>
+      </c>
+      <c r="C68" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D68" s="6" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/historico_fma.xlsx
+++ b/docs/historico_fma.xlsx
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em 23/10/2026 às 15:02 (Brasília). Uma aba por município.</t>
+          <t>Gerado em 23/10/2026 às 17:27 (Brasília). Uma aba por município.</t>
         </is>
       </c>
     </row>

--- a/docs/historico_fma.xlsx
+++ b/docs/historico_fma.xlsx
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em 23/10/2026 às 17:27 (Brasília). Uma aba por município.</t>
+          <t>Gerado em 24/10/2026 às 14:54 (Brasília). Uma aba por município.</t>
         </is>
       </c>
     </row>
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1933,20 +1933,40 @@
         <v>46318</v>
       </c>
       <c r="B68" s="5" t="n">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="C68" s="5" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="D68" s="6" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="E68" s="8" t="inlineStr">
-        <is>
-          <t>Médio</t>
+        <v>2.76</v>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="C69" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D69" s="6" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1959,7 +1979,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3329,13 +3349,13 @@
         <v>46318</v>
       </c>
       <c r="B68" s="5" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C68" s="5" t="n">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="D68" s="6" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
@@ -3343,6 +3363,26 @@
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="C69" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D69" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3355,7 +3395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4725,13 +4765,13 @@
         <v>46318</v>
       </c>
       <c r="B68" s="5" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C68" s="5" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="D68" s="6" t="n">
-        <v>6.37</v>
+        <v>4.87</v>
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
@@ -4739,6 +4779,26 @@
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="C69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="6" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4751,7 +4811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6121,13 +6181,13 @@
         <v>46318</v>
       </c>
       <c r="B68" s="5" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C68" s="5" t="n">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="D68" s="6" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
@@ -6135,6 +6195,26 @@
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="C69" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D69" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6147,7 +6227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7517,13 +7597,13 @@
         <v>46318</v>
       </c>
       <c r="B68" s="5" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C68" s="5" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="D68" s="6" t="n">
-        <v>3.37</v>
+        <v>3.38</v>
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
@@ -7531,6 +7611,26 @@
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="C69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="6" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7543,7 +7643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8913,13 +9013,13 @@
         <v>46318</v>
       </c>
       <c r="B68" s="5" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C68" s="5" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="D68" s="6" t="n">
-        <v>3.97</v>
+        <v>4.08</v>
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
@@ -8927,6 +9027,26 @@
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="C69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="6" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8939,7 +9059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10309,13 +10429,13 @@
         <v>46318</v>
       </c>
       <c r="B68" s="5" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C68" s="5" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="D68" s="6" t="n">
-        <v>3.71</v>
+        <v>3.64</v>
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
@@ -10323,6 +10443,26 @@
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="C69" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D69" s="6" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10335,7 +10475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11705,13 +11845,13 @@
         <v>46318</v>
       </c>
       <c r="B68" s="5" t="n">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C68" s="5" t="n">
-        <v>5.7</v>
+        <v>6.3</v>
       </c>
       <c r="D68" s="6" t="n">
-        <v>4.9</v>
+        <v>4.77</v>
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
@@ -11719,6 +11859,26 @@
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="C69" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D69" s="6" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11731,7 +11891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13101,20 +13261,40 @@
         <v>46318</v>
       </c>
       <c r="B68" s="5" t="n">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="C68" s="5" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="D68" s="6" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="E68" s="8" t="inlineStr">
-        <is>
-          <t>Médio</t>
+        <v>2.76</v>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="C69" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D69" s="6" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13127,7 +13307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14497,13 +14677,13 @@
         <v>46318</v>
       </c>
       <c r="B68" s="5" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C68" s="5" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="D68" s="6" t="n">
-        <v>3.97</v>
+        <v>4.08</v>
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
@@ -14511,6 +14691,26 @@
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="C69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="6" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14523,7 +14723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15893,13 +16093,13 @@
         <v>46318</v>
       </c>
       <c r="B68" s="5" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C68" s="5" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="D68" s="6" t="n">
-        <v>6.37</v>
+        <v>4.87</v>
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
@@ -15907,6 +16107,26 @@
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="C69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="6" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15919,7 +16139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17029,13 +17249,13 @@
         <v>46318</v>
       </c>
       <c r="B55" s="5" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C55" s="5" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="D55" s="6" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
@@ -17043,6 +17263,26 @@
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="6" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="E56" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17055,7 +17295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18425,20 +18665,40 @@
         <v>46318</v>
       </c>
       <c r="B68" s="5" t="n">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="C68" s="5" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="D68" s="6" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="E68" s="8" t="inlineStr">
-        <is>
-          <t>Médio</t>
+        <v>2.76</v>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="C69" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D69" s="6" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18451,7 +18711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19821,13 +20081,13 @@
         <v>46318</v>
       </c>
       <c r="B68" s="5" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C68" s="5" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="D68" s="6" t="n">
-        <v>2.82</v>
+        <v>2.71</v>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
@@ -19835,6 +20095,26 @@
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="C69" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D69" s="6" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -19847,7 +20127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21217,13 +21497,13 @@
         <v>46318</v>
       </c>
       <c r="B68" s="5" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C68" s="5" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="D68" s="6" t="n">
-        <v>6.37</v>
+        <v>4.87</v>
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
@@ -21231,6 +21511,26 @@
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="C69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="6" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/historico_fma.xlsx
+++ b/docs/historico_fma.xlsx
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em 24/10/2026 às 14:54 (Brasília). Uma aba por município.</t>
+          <t>Gerado em 24/10/2026 às 17:18 (Brasília). Uma aba por município.</t>
         </is>
       </c>
     </row>

--- a/docs/historico_fma.xlsx
+++ b/docs/historico_fma.xlsx
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em 24/10/2026 às 17:18 (Brasília). Uma aba por município.</t>
+          <t>Gerado em 25/10/2026 às 14:58 (Brasília). Uma aba por município.</t>
         </is>
       </c>
     </row>
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1953,13 +1953,13 @@
         <v>46319</v>
       </c>
       <c r="B69" s="5" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C69" s="5" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="D69" s="6" t="n">
-        <v>4.62</v>
+        <v>4.46</v>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
@@ -1967,6 +1967,26 @@
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B70" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="C70" s="5" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="D70" s="6" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1979,7 +1999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3369,13 +3389,13 @@
         <v>46319</v>
       </c>
       <c r="B69" s="5" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C69" s="5" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="D69" s="6" t="n">
-        <v>4.4</v>
+        <v>4.43</v>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
@@ -3383,6 +3403,26 @@
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B70" s="5" t="n">
+        <v>98</v>
+      </c>
+      <c r="C70" s="5" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="D70" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3395,7 +3435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4785,13 +4825,13 @@
         <v>46319</v>
       </c>
       <c r="B69" s="5" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C69" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D69" s="6" t="n">
-        <v>6.83</v>
+        <v>6.79</v>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
@@ -4799,6 +4839,26 @@
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B70" s="5" t="n">
+        <v>98</v>
+      </c>
+      <c r="C70" s="5" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="D70" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4811,7 +4871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6201,13 +6261,13 @@
         <v>46319</v>
       </c>
       <c r="B69" s="5" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C69" s="5" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="D69" s="6" t="n">
-        <v>4.4</v>
+        <v>4.43</v>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
@@ -6215,6 +6275,26 @@
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B70" s="5" t="n">
+        <v>98</v>
+      </c>
+      <c r="C70" s="5" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="D70" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6227,7 +6307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7617,13 +7697,13 @@
         <v>46319</v>
       </c>
       <c r="B69" s="5" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C69" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D69" s="6" t="n">
-        <v>4.63</v>
+        <v>4.58</v>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
@@ -7631,6 +7711,26 @@
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B70" s="5" t="n">
+        <v>96</v>
+      </c>
+      <c r="C70" s="5" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="D70" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7643,7 +7743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9048,6 +9148,26 @@
       </c>
       <c r="F69" t="inlineStr"/>
     </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B70" s="5" t="n">
+        <v>98</v>
+      </c>
+      <c r="C70" s="5" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="D70" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9059,7 +9179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10449,13 +10569,13 @@
         <v>46319</v>
       </c>
       <c r="B69" s="5" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C69" s="5" t="n">
         <v>1.2</v>
       </c>
       <c r="D69" s="6" t="n">
-        <v>5.39</v>
+        <v>5.42</v>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
@@ -10463,6 +10583,26 @@
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B70" s="5" t="n">
+        <v>96</v>
+      </c>
+      <c r="C70" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D70" s="6" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10475,7 +10615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11880,6 +12020,26 @@
       </c>
       <c r="F69" t="inlineStr"/>
     </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B70" s="5" t="n">
+        <v>86</v>
+      </c>
+      <c r="C70" s="5" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="D70" s="6" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11891,7 +12051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13281,13 +13441,13 @@
         <v>46319</v>
       </c>
       <c r="B69" s="5" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C69" s="5" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="D69" s="6" t="n">
-        <v>4.62</v>
+        <v>4.46</v>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
@@ -13295,6 +13455,26 @@
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B70" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="C70" s="5" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="D70" s="6" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13307,7 +13487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14712,6 +14892,26 @@
       </c>
       <c r="F69" t="inlineStr"/>
     </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B70" s="5" t="n">
+        <v>98</v>
+      </c>
+      <c r="C70" s="5" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="D70" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14723,7 +14923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16113,13 +16313,13 @@
         <v>46319</v>
       </c>
       <c r="B69" s="5" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C69" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D69" s="6" t="n">
-        <v>6.83</v>
+        <v>6.79</v>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
@@ -16127,6 +16327,26 @@
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B70" s="5" t="n">
+        <v>98</v>
+      </c>
+      <c r="C70" s="5" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="D70" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16139,7 +16359,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17269,13 +17489,13 @@
         <v>46319</v>
       </c>
       <c r="B56" s="5" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C56" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D56" s="6" t="n">
-        <v>3.66</v>
+        <v>3.61</v>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
@@ -17283,6 +17503,26 @@
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="D57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17295,7 +17535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18685,13 +18925,13 @@
         <v>46319</v>
       </c>
       <c r="B69" s="5" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C69" s="5" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="D69" s="6" t="n">
-        <v>4.62</v>
+        <v>4.46</v>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
@@ -18699,6 +18939,26 @@
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B70" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="C70" s="5" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="D70" s="6" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18711,7 +18971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20101,13 +20361,13 @@
         <v>46319</v>
       </c>
       <c r="B69" s="5" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C69" s="5" t="n">
         <v>0.3</v>
       </c>
       <c r="D69" s="6" t="n">
-        <v>4.43</v>
+        <v>4.46</v>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
@@ -20115,6 +20375,26 @@
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B70" s="5" t="n">
+        <v>96</v>
+      </c>
+      <c r="C70" s="5" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="D70" s="6" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -20127,7 +20407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21517,13 +21797,13 @@
         <v>46319</v>
       </c>
       <c r="B69" s="5" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C69" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D69" s="6" t="n">
-        <v>6.83</v>
+        <v>6.79</v>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
@@ -21531,6 +21811,26 @@
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B70" s="5" t="n">
+        <v>98</v>
+      </c>
+      <c r="C70" s="5" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="D70" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/historico_fma.xlsx
+++ b/docs/historico_fma.xlsx
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em 25/10/2026 às 14:58 (Brasília). Uma aba por município.</t>
+          <t>Gerado em 25/10/2026 às 17:21 (Brasília). Uma aba por município.</t>
         </is>
       </c>
     </row>

--- a/docs/historico_fma.xlsx
+++ b/docs/historico_fma.xlsx
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em 25/10/2026 às 17:21 (Brasília). Uma aba por município.</t>
+          <t>Gerado em 26/10/2026 às 15:09 (Brasília). Uma aba por município.</t>
         </is>
       </c>
     </row>
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1976,17 +1976,37 @@
         <v>95</v>
       </c>
       <c r="C70" s="5" t="n">
-        <v>12.2</v>
+        <v>19.8</v>
       </c>
       <c r="D70" s="6" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="E70" s="7" t="inlineStr">
-        <is>
-          <t>Pequeno</t>
+        <v>0</v>
+      </c>
+      <c r="E70" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B71" s="5" t="n">
+        <v>89</v>
+      </c>
+      <c r="C71" s="5" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="D71" s="6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1999,7 +2019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3409,10 +3429,10 @@
         <v>46320</v>
       </c>
       <c r="B70" s="5" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C70" s="5" t="n">
-        <v>18.3</v>
+        <v>24.5</v>
       </c>
       <c r="D70" s="6" t="n">
         <v>0</v>
@@ -3423,6 +3443,26 @@
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B71" s="5" t="n">
+        <v>82</v>
+      </c>
+      <c r="C71" s="5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="D71" s="6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3435,7 +3475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4845,10 +4885,10 @@
         <v>46320</v>
       </c>
       <c r="B70" s="5" t="n">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="C70" s="5" t="n">
-        <v>18.3</v>
+        <v>18.1</v>
       </c>
       <c r="D70" s="6" t="n">
         <v>0</v>
@@ -4859,6 +4899,26 @@
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B71" s="5" t="n">
+        <v>86</v>
+      </c>
+      <c r="C71" s="5" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="D71" s="6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4871,7 +4931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6281,10 +6341,10 @@
         <v>46320</v>
       </c>
       <c r="B70" s="5" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C70" s="5" t="n">
-        <v>18.3</v>
+        <v>24.5</v>
       </c>
       <c r="D70" s="6" t="n">
         <v>0</v>
@@ -6295,6 +6355,26 @@
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B71" s="5" t="n">
+        <v>82</v>
+      </c>
+      <c r="C71" s="5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="D71" s="6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6307,7 +6387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7717,10 +7797,10 @@
         <v>46320</v>
       </c>
       <c r="B70" s="5" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C70" s="5" t="n">
-        <v>20.7</v>
+        <v>19.1</v>
       </c>
       <c r="D70" s="6" t="n">
         <v>0</v>
@@ -7731,6 +7811,26 @@
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B71" s="5" t="n">
+        <v>88</v>
+      </c>
+      <c r="C71" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="D71" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7743,7 +7843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9153,10 +9253,10 @@
         <v>46320</v>
       </c>
       <c r="B70" s="5" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C70" s="5" t="n">
-        <v>18.1</v>
+        <v>21.1</v>
       </c>
       <c r="D70" s="6" t="n">
         <v>0</v>
@@ -9167,6 +9267,26 @@
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B71" s="5" t="n">
+        <v>81</v>
+      </c>
+      <c r="C71" s="5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="D71" s="6" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9179,7 +9299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10589,20 +10709,40 @@
         <v>46320</v>
       </c>
       <c r="B70" s="5" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C70" s="5" t="n">
-        <v>10</v>
+        <v>14.7</v>
       </c>
       <c r="D70" s="6" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="E70" s="7" t="inlineStr">
-        <is>
-          <t>Pequeno</t>
+        <v>0</v>
+      </c>
+      <c r="E70" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B71" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="C71" s="5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D71" s="6" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10615,7 +10755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12025,20 +12165,40 @@
         <v>46320</v>
       </c>
       <c r="B70" s="5" t="n">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="C70" s="5" t="n">
-        <v>12.4</v>
+        <v>18.8</v>
       </c>
       <c r="D70" s="6" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="E70" s="7" t="inlineStr">
-        <is>
-          <t>Pequeno</t>
+        <v>0</v>
+      </c>
+      <c r="E70" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B71" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="C71" s="5" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="D71" s="6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12051,7 +12211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13464,17 +13624,37 @@
         <v>95</v>
       </c>
       <c r="C70" s="5" t="n">
-        <v>12.2</v>
+        <v>19.8</v>
       </c>
       <c r="D70" s="6" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="E70" s="7" t="inlineStr">
-        <is>
-          <t>Pequeno</t>
+        <v>0</v>
+      </c>
+      <c r="E70" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B71" s="5" t="n">
+        <v>89</v>
+      </c>
+      <c r="C71" s="5" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="D71" s="6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13487,7 +13667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14897,10 +15077,10 @@
         <v>46320</v>
       </c>
       <c r="B70" s="5" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C70" s="5" t="n">
-        <v>18.1</v>
+        <v>21.1</v>
       </c>
       <c r="D70" s="6" t="n">
         <v>0</v>
@@ -14911,6 +15091,26 @@
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B71" s="5" t="n">
+        <v>81</v>
+      </c>
+      <c r="C71" s="5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="D71" s="6" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14923,7 +15123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16333,10 +16533,10 @@
         <v>46320</v>
       </c>
       <c r="B70" s="5" t="n">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="C70" s="5" t="n">
-        <v>18.3</v>
+        <v>18.1</v>
       </c>
       <c r="D70" s="6" t="n">
         <v>0</v>
@@ -16347,6 +16547,26 @@
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B71" s="5" t="n">
+        <v>86</v>
+      </c>
+      <c r="C71" s="5" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="D71" s="6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16359,7 +16579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17509,10 +17729,10 @@
         <v>46320</v>
       </c>
       <c r="B57" s="5" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C57" s="5" t="n">
-        <v>25.7</v>
+        <v>23.4</v>
       </c>
       <c r="D57" s="6" t="n">
         <v>0</v>
@@ -17523,6 +17743,26 @@
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>91</v>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="D58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17535,7 +17775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18948,17 +19188,37 @@
         <v>95</v>
       </c>
       <c r="C70" s="5" t="n">
-        <v>12.2</v>
+        <v>19.8</v>
       </c>
       <c r="D70" s="6" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="E70" s="7" t="inlineStr">
-        <is>
-          <t>Pequeno</t>
+        <v>0</v>
+      </c>
+      <c r="E70" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B71" s="5" t="n">
+        <v>89</v>
+      </c>
+      <c r="C71" s="5" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="D71" s="6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18971,7 +19231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20381,20 +20641,40 @@
         <v>46320</v>
       </c>
       <c r="B70" s="5" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C70" s="5" t="n">
-        <v>12.4</v>
+        <v>21.1</v>
       </c>
       <c r="D70" s="6" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="E70" s="7" t="inlineStr">
-        <is>
-          <t>Pequeno</t>
+        <v>0</v>
+      </c>
+      <c r="E70" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B71" s="5" t="n">
+        <v>91</v>
+      </c>
+      <c r="C71" s="5" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="D71" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -20407,7 +20687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21817,10 +22097,10 @@
         <v>46320</v>
       </c>
       <c r="B70" s="5" t="n">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="C70" s="5" t="n">
-        <v>18.3</v>
+        <v>18.1</v>
       </c>
       <c r="D70" s="6" t="n">
         <v>0</v>
@@ -21831,6 +22111,26 @@
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B71" s="5" t="n">
+        <v>86</v>
+      </c>
+      <c r="C71" s="5" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="D71" s="6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/historico_fma.xlsx
+++ b/docs/historico_fma.xlsx
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em 26/10/2026 às 15:09 (Brasília). Uma aba por município.</t>
+          <t>Gerado em 26/10/2026 às 17:29 (Brasília). Uma aba por município.</t>
         </is>
       </c>
     </row>

--- a/docs/historico_fma.xlsx
+++ b/docs/historico_fma.xlsx
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em 26/10/2026 às 17:29 (Brasília). Uma aba por município.</t>
+          <t>Gerado em 27/10/2026 às 15:12 (Brasília). Uma aba por município.</t>
         </is>
       </c>
     </row>
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1993,13 +1993,13 @@
         <v>46321</v>
       </c>
       <c r="B71" s="5" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C71" s="5" t="n">
-        <v>10.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D71" s="6" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
@@ -2007,6 +2007,26 @@
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="C72" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D72" s="6" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2019,7 +2039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3449,13 +3469,13 @@
         <v>46321</v>
       </c>
       <c r="B71" s="5" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C71" s="5" t="n">
         <v>7.6</v>
       </c>
       <c r="D71" s="6" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
@@ -3463,6 +3483,26 @@
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="C72" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D72" s="6" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3475,7 +3515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4905,13 +4945,13 @@
         <v>46321</v>
       </c>
       <c r="B71" s="5" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C71" s="5" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="D71" s="6" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
@@ -4919,6 +4959,26 @@
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="C72" s="5" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D72" s="6" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4931,7 +4991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6361,13 +6421,13 @@
         <v>46321</v>
       </c>
       <c r="B71" s="5" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C71" s="5" t="n">
         <v>7.6</v>
       </c>
       <c r="D71" s="6" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
@@ -6375,6 +6435,26 @@
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="C72" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D72" s="6" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6387,7 +6467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7820,7 +7900,7 @@
         <v>88</v>
       </c>
       <c r="C71" s="5" t="n">
-        <v>18</v>
+        <v>18.6</v>
       </c>
       <c r="D71" s="6" t="n">
         <v>0</v>
@@ -7831,6 +7911,26 @@
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="C72" s="5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="D72" s="6" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7843,7 +7943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9276,7 +9376,7 @@
         <v>81</v>
       </c>
       <c r="C71" s="5" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="D71" s="6" t="n">
         <v>1.23</v>
@@ -9287,6 +9387,26 @@
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="C72" s="5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="D72" s="6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9299,7 +9419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10729,13 +10849,13 @@
         <v>46321</v>
       </c>
       <c r="B71" s="5" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C71" s="5" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="D71" s="6" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
@@ -10743,6 +10863,26 @@
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="C72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="6" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="E72" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10755,7 +10895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12185,13 +12325,13 @@
         <v>46321</v>
       </c>
       <c r="B71" s="5" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C71" s="5" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D71" s="6" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
@@ -12199,6 +12339,26 @@
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="C72" s="5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D72" s="6" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12211,7 +12371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13641,13 +13801,13 @@
         <v>46321</v>
       </c>
       <c r="B71" s="5" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C71" s="5" t="n">
-        <v>10.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D71" s="6" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
@@ -13655,6 +13815,26 @@
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="C72" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D72" s="6" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13667,7 +13847,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15100,7 +15280,7 @@
         <v>81</v>
       </c>
       <c r="C71" s="5" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="D71" s="6" t="n">
         <v>1.23</v>
@@ -15111,6 +15291,26 @@
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="C72" s="5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="D72" s="6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15123,7 +15323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16553,13 +16753,13 @@
         <v>46321</v>
       </c>
       <c r="B71" s="5" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C71" s="5" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="D71" s="6" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
@@ -16567,6 +16767,26 @@
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="C72" s="5" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D72" s="6" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16579,7 +16799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17752,7 +17972,7 @@
         <v>91</v>
       </c>
       <c r="C58" s="5" t="n">
-        <v>24</v>
+        <v>20.6</v>
       </c>
       <c r="D58" s="6" t="n">
         <v>0</v>
@@ -17763,6 +17983,26 @@
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B59" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="C59" s="5" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="D59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17775,7 +18015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19205,13 +19445,13 @@
         <v>46321</v>
       </c>
       <c r="B71" s="5" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C71" s="5" t="n">
-        <v>10.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D71" s="6" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
@@ -19219,6 +19459,26 @@
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="C72" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D72" s="6" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -19231,7 +19491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20664,7 +20924,7 @@
         <v>91</v>
       </c>
       <c r="C71" s="5" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="D71" s="6" t="n">
         <v>0</v>
@@ -20675,6 +20935,26 @@
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="C72" s="5" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="D72" s="6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -20687,7 +20967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22117,13 +22397,13 @@
         <v>46321</v>
       </c>
       <c r="B71" s="5" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C71" s="5" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="D71" s="6" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
@@ -22131,6 +22411,26 @@
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="C72" s="5" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D72" s="6" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/historico_fma.xlsx
+++ b/docs/historico_fma.xlsx
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em 27/10/2026 às 15:12 (Brasília). Uma aba por município.</t>
+          <t>Gerado em 27/10/2026 às 17:34 (Brasília). Uma aba por município.</t>
         </is>
       </c>
     </row>

--- a/docs/historico_fma.xlsx
+++ b/docs/historico_fma.xlsx
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em 27/10/2026 às 17:34 (Brasília). Uma aba por município.</t>
+          <t>Gerado em 28/10/2026 às 15:14 (Brasília). Uma aba por município.</t>
         </is>
       </c>
     </row>
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2016,10 +2016,10 @@
         <v>73</v>
       </c>
       <c r="C72" s="5" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>2.47</v>
+        <v>2.14</v>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
@@ -2027,6 +2027,26 @@
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="C73" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D73" s="6" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2039,7 +2059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3489,13 +3509,13 @@
         <v>46322</v>
       </c>
       <c r="B72" s="5" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C72" s="5" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
@@ -3503,6 +3523,26 @@
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="C73" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D73" s="6" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3515,7 +3555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4965,13 +5005,13 @@
         <v>46322</v>
       </c>
       <c r="B72" s="5" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C72" s="5" t="n">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>1.93</v>
+        <v>1.64</v>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
@@ -4979,6 +5019,26 @@
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="C73" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" s="6" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4991,7 +5051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6441,13 +6501,13 @@
         <v>46322</v>
       </c>
       <c r="B72" s="5" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C72" s="5" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
@@ -6455,6 +6515,26 @@
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="C73" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D73" s="6" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6467,7 +6547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7917,13 +7997,13 @@
         <v>46322</v>
       </c>
       <c r="B72" s="5" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C72" s="5" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
@@ -7931,6 +8011,26 @@
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="C73" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="6" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7943,7 +8043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9393,13 +9493,13 @@
         <v>46322</v>
       </c>
       <c r="B72" s="5" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C72" s="5" t="n">
-        <v>2.7</v>
+        <v>4.4</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
@@ -9407,6 +9507,26 @@
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="C73" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D73" s="6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9419,7 +9539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10869,13 +10989,13 @@
         <v>46322</v>
       </c>
       <c r="B72" s="5" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C72" s="5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>3.26</v>
+        <v>3.16</v>
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
@@ -10883,6 +11003,26 @@
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="C73" s="5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D73" s="6" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10895,7 +11035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12345,13 +12485,13 @@
         <v>46322</v>
       </c>
       <c r="B72" s="5" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C72" s="5" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
@@ -12359,6 +12499,26 @@
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="C73" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D73" s="6" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12371,7 +12531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13824,10 +13984,10 @@
         <v>73</v>
       </c>
       <c r="C72" s="5" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>2.47</v>
+        <v>2.14</v>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
@@ -13835,6 +13995,26 @@
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="C73" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D73" s="6" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13847,7 +14027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15297,13 +15477,13 @@
         <v>46322</v>
       </c>
       <c r="B72" s="5" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C72" s="5" t="n">
-        <v>2.7</v>
+        <v>4.4</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
@@ -15311,6 +15491,26 @@
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="C73" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D73" s="6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15323,7 +15523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16773,13 +16973,13 @@
         <v>46322</v>
       </c>
       <c r="B72" s="5" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C72" s="5" t="n">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>1.93</v>
+        <v>1.64</v>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
@@ -16787,6 +16987,26 @@
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="C73" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" s="6" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16799,7 +17019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17989,10 +18209,10 @@
         <v>46322</v>
       </c>
       <c r="B59" s="5" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="C59" s="5" t="n">
-        <v>13.9</v>
+        <v>14.5</v>
       </c>
       <c r="D59" s="6" t="n">
         <v>0</v>
@@ -18003,6 +18223,26 @@
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D60" s="6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18015,7 +18255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19468,10 +19708,10 @@
         <v>73</v>
       </c>
       <c r="C72" s="5" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>2.47</v>
+        <v>2.14</v>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
@@ -19479,6 +19719,26 @@
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="C73" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D73" s="6" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -19491,7 +19751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20941,13 +21201,13 @@
         <v>46322</v>
       </c>
       <c r="B72" s="5" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C72" s="5" t="n">
         <v>10.1</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
@@ -20955,6 +21215,26 @@
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="C73" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D73" s="6" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -20967,7 +21247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22417,13 +22697,13 @@
         <v>46322</v>
       </c>
       <c r="B72" s="5" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C72" s="5" t="n">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>1.93</v>
+        <v>1.64</v>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
@@ -22431,6 +22711,26 @@
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="C73" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" s="6" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/historico_fma.xlsx
+++ b/docs/historico_fma.xlsx
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em 28/10/2026 às 15:14 (Brasília). Uma aba por município.</t>
+          <t>Gerado em 28/10/2026 às 17:37 (Brasília). Uma aba por município.</t>
         </is>
       </c>
     </row>
@@ -9513,13 +9513,13 @@
         <v>46323</v>
       </c>
       <c r="B73" s="5" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C73" s="5" t="n">
         <v>0.4</v>
       </c>
       <c r="D73" s="6" t="n">
-        <v>4.2</v>
+        <v>4.13</v>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>

--- a/docs/historico_fma.xlsx
+++ b/docs/historico_fma.xlsx
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em 28/10/2026 às 17:37 (Brasília). Uma aba por município.</t>
+          <t>Gerado em 29/10/2026 às 15:15 (Brasília). Uma aba por município.</t>
         </is>
       </c>
     </row>
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2048,6 +2048,26 @@
       </c>
       <c r="F73" t="inlineStr"/>
     </row>
+    <row r="74">
+      <c r="A74" s="4" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="C74" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" s="6" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2059,7 +2079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3532,7 +3552,7 @@
         <v>68</v>
       </c>
       <c r="C73" s="5" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="D73" s="6" t="n">
         <v>4.07</v>
@@ -3543,6 +3563,26 @@
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>91</v>
+      </c>
+      <c r="C74" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D74" s="6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3555,7 +3595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5025,13 +5065,13 @@
         <v>46323</v>
       </c>
       <c r="B73" s="5" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C73" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D73" s="6" t="n">
-        <v>3.33</v>
+        <v>3.45</v>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
@@ -5039,6 +5079,26 @@
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>79</v>
+      </c>
+      <c r="C74" s="5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D74" s="6" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5051,7 +5111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6524,7 +6584,7 @@
         <v>68</v>
       </c>
       <c r="C73" s="5" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="D73" s="6" t="n">
         <v>4.07</v>
@@ -6535,6 +6595,26 @@
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>91</v>
+      </c>
+      <c r="C74" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D74" s="6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6547,7 +6627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8017,13 +8097,13 @@
         <v>46323</v>
       </c>
       <c r="B73" s="5" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C73" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="6" t="n">
-        <v>3.11</v>
+        <v>3.13</v>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
@@ -8031,6 +8111,26 @@
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>92</v>
+      </c>
+      <c r="C74" s="5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="D74" s="6" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8043,7 +8143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9528,6 +9628,26 @@
       </c>
       <c r="F73" t="inlineStr"/>
     </row>
+    <row r="74">
+      <c r="A74" s="4" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>81</v>
+      </c>
+      <c r="C74" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D74" s="6" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9539,7 +9659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11009,13 +11129,13 @@
         <v>46323</v>
       </c>
       <c r="B73" s="5" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="D73" s="6" t="n">
-        <v>3.62</v>
+        <v>4.55</v>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
@@ -11023,6 +11143,26 @@
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="C74" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D74" s="6" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11035,7 +11175,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12505,13 +12645,13 @@
         <v>46323</v>
       </c>
       <c r="B73" s="5" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C73" s="5" t="n">
         <v>0.5</v>
       </c>
       <c r="D73" s="6" t="n">
-        <v>4.38</v>
+        <v>4.27</v>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
@@ -12519,6 +12659,26 @@
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>88</v>
+      </c>
+      <c r="C74" s="5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D74" s="6" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12531,7 +12691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14016,6 +14176,26 @@
       </c>
       <c r="F73" t="inlineStr"/>
     </row>
+    <row r="74">
+      <c r="A74" s="4" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="C74" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" s="6" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14027,7 +14207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15497,13 +15677,13 @@
         <v>46323</v>
       </c>
       <c r="B73" s="5" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C73" s="5" t="n">
         <v>0.4</v>
       </c>
       <c r="D73" s="6" t="n">
-        <v>4.2</v>
+        <v>4.13</v>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
@@ -15511,6 +15691,26 @@
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>81</v>
+      </c>
+      <c r="C74" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D74" s="6" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15523,7 +15723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16993,13 +17193,13 @@
         <v>46323</v>
       </c>
       <c r="B73" s="5" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C73" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D73" s="6" t="n">
-        <v>3.33</v>
+        <v>3.45</v>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
@@ -17007,6 +17207,26 @@
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>79</v>
+      </c>
+      <c r="C74" s="5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D74" s="6" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17019,7 +17239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18229,13 +18449,13 @@
         <v>46323</v>
       </c>
       <c r="B60" s="5" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C60" s="5" t="n">
         <v>0.9</v>
       </c>
       <c r="D60" s="6" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
@@ -18243,6 +18463,26 @@
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D61" s="6" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18255,7 +18495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19740,6 +19980,26 @@
       </c>
       <c r="F73" t="inlineStr"/>
     </row>
+    <row r="74">
+      <c r="A74" s="4" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="C74" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" s="6" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19751,7 +20011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21221,13 +21481,13 @@
         <v>46323</v>
       </c>
       <c r="B73" s="5" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C73" s="5" t="n">
         <v>0.6</v>
       </c>
       <c r="D73" s="6" t="n">
-        <v>3.08</v>
+        <v>3.03</v>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
@@ -21235,6 +21495,26 @@
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="C74" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D74" s="6" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -21247,7 +21527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22717,13 +22997,13 @@
         <v>46323</v>
       </c>
       <c r="B73" s="5" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C73" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D73" s="6" t="n">
-        <v>3.33</v>
+        <v>3.45</v>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
@@ -22731,6 +23011,26 @@
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>79</v>
+      </c>
+      <c r="C74" s="5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D74" s="6" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/historico_fma.xlsx
+++ b/docs/historico_fma.xlsx
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em 29/10/2026 às 15:15 (Brasília). Uma aba por município.</t>
+          <t>Gerado em 29/10/2026 às 17:37 (Brasília). Uma aba por município.</t>
         </is>
       </c>
     </row>
@@ -2053,13 +2053,13 @@
         <v>46324</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C74" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>4.95</v>
+        <v>4.99</v>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
@@ -3569,13 +3569,13 @@
         <v>46324</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C74" s="5" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>3.95</v>
+        <v>5.28</v>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
@@ -5085,13 +5085,13 @@
         <v>46324</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C74" s="5" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>4.72</v>
+        <v>4.75</v>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
@@ -6601,13 +6601,13 @@
         <v>46324</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C74" s="5" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>3.95</v>
+        <v>5.28</v>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
@@ -8117,13 +8117,13 @@
         <v>46324</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C74" s="5" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>4.22</v>
+        <v>4.24</v>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
@@ -9633,13 +9633,13 @@
         <v>46324</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C74" s="5" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>5.37</v>
+        <v>5.41</v>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
@@ -11149,13 +11149,13 @@
         <v>46324</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C74" s="5" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>5.92</v>
+        <v>5.9</v>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
@@ -12665,13 +12665,13 @@
         <v>46324</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="C74" s="5" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>4.13</v>
+        <v>5.68</v>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
@@ -14181,13 +14181,13 @@
         <v>46324</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C74" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>4.95</v>
+        <v>4.99</v>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
@@ -15697,13 +15697,13 @@
         <v>46324</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C74" s="5" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>5.37</v>
+        <v>5.41</v>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
@@ -17213,13 +17213,13 @@
         <v>46324</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C74" s="5" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>4.72</v>
+        <v>4.75</v>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
@@ -18469,13 +18469,13 @@
         <v>46324</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C61" s="5" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="D61" s="6" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
@@ -19985,13 +19985,13 @@
         <v>46324</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C74" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>4.95</v>
+        <v>4.99</v>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
@@ -21504,7 +21504,7 @@
         <v>77</v>
       </c>
       <c r="C74" s="5" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="D74" s="6" t="n">
         <v>4.33</v>
@@ -23017,13 +23017,13 @@
         <v>46324</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C74" s="5" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>4.72</v>
+        <v>4.75</v>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>

--- a/docs/historico_fma.xlsx
+++ b/docs/historico_fma.xlsx
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em 29/10/2026 às 17:37 (Brasília). Uma aba por município.</t>
+          <t>Gerado em 30/10/2026 às 15:08 (Brasília). Uma aba por município.</t>
         </is>
       </c>
     </row>
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2053,13 +2053,13 @@
         <v>46324</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C74" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>4.99</v>
+        <v>4.95</v>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
@@ -2067,6 +2067,26 @@
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="D75" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2079,7 +2099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3569,13 +3589,13 @@
         <v>46324</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C74" s="5" t="n">
         <v>2.2</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>5.28</v>
+        <v>5.26</v>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
@@ -3583,6 +3603,26 @@
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>79</v>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D75" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3595,7 +3635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5085,13 +5125,13 @@
         <v>46324</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C74" s="5" t="n">
         <v>0.4</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>4.75</v>
+        <v>4.77</v>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
@@ -5099,6 +5139,26 @@
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="D75" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5111,7 +5171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6601,13 +6661,13 @@
         <v>46324</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C74" s="5" t="n">
         <v>2.2</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>5.28</v>
+        <v>5.26</v>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
@@ -6615,6 +6675,26 @@
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>79</v>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D75" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6627,7 +6707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8132,6 +8212,26 @@
       </c>
       <c r="F74" t="inlineStr"/>
     </row>
+    <row r="75">
+      <c r="A75" s="4" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>84</v>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="D75" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8143,7 +8243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9633,13 +9733,13 @@
         <v>46324</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C74" s="5" t="n">
         <v>1.9</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>5.41</v>
+        <v>5.43</v>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
@@ -9647,6 +9747,26 @@
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="D75" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9659,7 +9779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11149,13 +11269,13 @@
         <v>46324</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C74" s="5" t="n">
         <v>0.4</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>5.9</v>
+        <v>5.87</v>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
@@ -11163,6 +11283,26 @@
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="D75" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11175,7 +11315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12665,13 +12805,13 @@
         <v>46324</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C74" s="5" t="n">
         <v>1.5</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>5.68</v>
+        <v>5.66</v>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
@@ -12679,6 +12819,26 @@
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="D75" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12691,7 +12851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14181,13 +14341,13 @@
         <v>46324</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C74" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>4.99</v>
+        <v>4.95</v>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
@@ -14195,6 +14355,26 @@
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="D75" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14207,7 +14387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15697,13 +15877,13 @@
         <v>46324</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C74" s="5" t="n">
         <v>1.9</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>5.41</v>
+        <v>5.43</v>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
@@ -15711,6 +15891,26 @@
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="D75" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15723,7 +15923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17213,13 +17413,13 @@
         <v>46324</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C74" s="5" t="n">
         <v>0.4</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>4.75</v>
+        <v>4.77</v>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
@@ -17227,6 +17427,26 @@
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="D75" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17239,7 +17459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18484,6 +18704,26 @@
       </c>
       <c r="F61" t="inlineStr"/>
     </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>79</v>
+      </c>
+      <c r="C62" s="5" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="D62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18495,7 +18735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19985,13 +20225,13 @@
         <v>46324</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C74" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>4.99</v>
+        <v>4.95</v>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
@@ -19999,6 +20239,26 @@
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="D75" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -20011,7 +20271,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21516,6 +21776,26 @@
       </c>
       <c r="F74" t="inlineStr"/>
     </row>
+    <row r="75">
+      <c r="A75" s="4" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>82</v>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="D75" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21527,7 +21807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -23017,13 +23297,13 @@
         <v>46324</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C74" s="5" t="n">
         <v>0.4</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>4.75</v>
+        <v>4.77</v>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
@@ -23031,6 +23311,26 @@
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="D75" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/historico_fma.xlsx
+++ b/docs/historico_fma.xlsx
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em 30/10/2026 às 15:08 (Brasília). Uma aba por município.</t>
+          <t>Gerado em 30/10/2026 às 17:34 (Brasília). Uma aba por município.</t>
         </is>
       </c>
     </row>
@@ -2073,10 +2073,10 @@
         <v>46325</v>
       </c>
       <c r="B75" s="5" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C75" s="5" t="n">
-        <v>23.2</v>
+        <v>23.4</v>
       </c>
       <c r="D75" s="6" t="n">
         <v>0</v>
@@ -3609,10 +3609,10 @@
         <v>46325</v>
       </c>
       <c r="B75" s="5" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C75" s="5" t="n">
-        <v>15</v>
+        <v>15.8</v>
       </c>
       <c r="D75" s="6" t="n">
         <v>0</v>
@@ -5145,10 +5145,10 @@
         <v>46325</v>
       </c>
       <c r="B75" s="5" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C75" s="5" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="D75" s="6" t="n">
         <v>0</v>
@@ -6681,10 +6681,10 @@
         <v>46325</v>
       </c>
       <c r="B75" s="5" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C75" s="5" t="n">
-        <v>15</v>
+        <v>15.8</v>
       </c>
       <c r="D75" s="6" t="n">
         <v>0</v>
@@ -8217,7 +8217,7 @@
         <v>46325</v>
       </c>
       <c r="B75" s="5" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C75" s="5" t="n">
         <v>17.2</v>
@@ -9753,10 +9753,10 @@
         <v>46325</v>
       </c>
       <c r="B75" s="5" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C75" s="5" t="n">
-        <v>18.3</v>
+        <v>17.2</v>
       </c>
       <c r="D75" s="6" t="n">
         <v>0</v>
@@ -11289,10 +11289,10 @@
         <v>46325</v>
       </c>
       <c r="B75" s="5" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C75" s="5" t="n">
-        <v>38.7</v>
+        <v>37.3</v>
       </c>
       <c r="D75" s="6" t="n">
         <v>0</v>
@@ -12828,7 +12828,7 @@
         <v>72</v>
       </c>
       <c r="C75" s="5" t="n">
-        <v>19.9</v>
+        <v>20.2</v>
       </c>
       <c r="D75" s="6" t="n">
         <v>0</v>
@@ -14361,10 +14361,10 @@
         <v>46325</v>
       </c>
       <c r="B75" s="5" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C75" s="5" t="n">
-        <v>23.2</v>
+        <v>23.4</v>
       </c>
       <c r="D75" s="6" t="n">
         <v>0</v>
@@ -15897,10 +15897,10 @@
         <v>46325</v>
       </c>
       <c r="B75" s="5" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C75" s="5" t="n">
-        <v>18.3</v>
+        <v>17.2</v>
       </c>
       <c r="D75" s="6" t="n">
         <v>0</v>
@@ -17433,10 +17433,10 @@
         <v>46325</v>
       </c>
       <c r="B75" s="5" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C75" s="5" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="D75" s="6" t="n">
         <v>0</v>
@@ -18709,10 +18709,10 @@
         <v>46325</v>
       </c>
       <c r="B62" s="5" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C62" s="5" t="n">
-        <v>14.3</v>
+        <v>14.1</v>
       </c>
       <c r="D62" s="6" t="n">
         <v>0</v>
@@ -20245,10 +20245,10 @@
         <v>46325</v>
       </c>
       <c r="B75" s="5" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C75" s="5" t="n">
-        <v>23.2</v>
+        <v>23.4</v>
       </c>
       <c r="D75" s="6" t="n">
         <v>0</v>
@@ -21781,10 +21781,10 @@
         <v>46325</v>
       </c>
       <c r="B75" s="5" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C75" s="5" t="n">
-        <v>35.4</v>
+        <v>34.2</v>
       </c>
       <c r="D75" s="6" t="n">
         <v>0</v>
@@ -23317,10 +23317,10 @@
         <v>46325</v>
       </c>
       <c r="B75" s="5" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C75" s="5" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="D75" s="6" t="n">
         <v>0</v>

--- a/docs/historico_fma.xlsx
+++ b/docs/historico_fma.xlsx
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em 30/10/2026 às 17:34 (Brasília). Uma aba por município.</t>
+          <t>Gerado em 31/10/2026 às 15:01 (Brasília). Uma aba por município.</t>
         </is>
       </c>
     </row>
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2073,7 +2073,7 @@
         <v>46325</v>
       </c>
       <c r="B75" s="5" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C75" s="5" t="n">
         <v>23.4</v>
@@ -2087,6 +2087,26 @@
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="n">
+        <v>46326</v>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="C76" s="5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="D76" s="6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2099,7 +2119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3609,7 +3629,7 @@
         <v>46325</v>
       </c>
       <c r="B75" s="5" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C75" s="5" t="n">
         <v>15.8</v>
@@ -3623,6 +3643,26 @@
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="n">
+        <v>46326</v>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="C76" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="D76" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3635,7 +3675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5160,6 +5200,26 @@
       </c>
       <c r="F75" t="inlineStr"/>
     </row>
+    <row r="76">
+      <c r="A76" s="4" t="n">
+        <v>46326</v>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="C76" s="5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D76" s="6" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5171,7 +5231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6681,7 +6741,7 @@
         <v>46325</v>
       </c>
       <c r="B75" s="5" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C75" s="5" t="n">
         <v>15.8</v>
@@ -6695,6 +6755,26 @@
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="n">
+        <v>46326</v>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="C76" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="D76" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" s="10" t="inlineStr">
+        <is>
+          <t>Nulo</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6707,7 +6787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8217,7 +8297,7 @@
         <v>46325</v>
       </c>
       <c r="B75" s="5" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C75" s="5" t="n">
         <v>17.2</v>
@@ -8231,6 +8311,26 @@
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="n">
+        <v>46326</v>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="C76" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D76" s="6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8243,7 +8343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9753,7 +9853,7 @@
         <v>46325</v>
       </c>
       <c r="B75" s="5" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C75" s="5" t="n">
         <v>17.2</v>
@@ -9767,6 +9867,26 @@
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="n">
+        <v>46326</v>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="C76" s="5" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D76" s="6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9779,7 +9899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11289,7 +11409,7 @@
         <v>46325</v>
       </c>
       <c r="B75" s="5" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C75" s="5" t="n">
         <v>37.3</v>
@@ -11303,6 +11423,26 @@
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="n">
+        <v>46326</v>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="C76" s="5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D76" s="6" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11315,7 +11455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12825,7 +12965,7 @@
         <v>46325</v>
       </c>
       <c r="B75" s="5" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C75" s="5" t="n">
         <v>20.2</v>
@@ -12839,6 +12979,26 @@
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="n">
+        <v>46326</v>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="C76" s="5" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="D76" s="6" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12851,7 +13011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14361,7 +14521,7 @@
         <v>46325</v>
       </c>
       <c r="B75" s="5" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C75" s="5" t="n">
         <v>23.4</v>
@@ -14375,6 +14535,26 @@
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="n">
+        <v>46326</v>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="C76" s="5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="D76" s="6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14387,7 +14567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15897,7 +16077,7 @@
         <v>46325</v>
       </c>
       <c r="B75" s="5" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C75" s="5" t="n">
         <v>17.2</v>
@@ -15911,6 +16091,26 @@
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="n">
+        <v>46326</v>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="C76" s="5" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D76" s="6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15923,7 +16123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17448,6 +17648,26 @@
       </c>
       <c r="F75" t="inlineStr"/>
     </row>
+    <row r="76">
+      <c r="A76" s="4" t="n">
+        <v>46326</v>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="C76" s="5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D76" s="6" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17459,7 +17679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18709,7 +18929,7 @@
         <v>46325</v>
       </c>
       <c r="B62" s="5" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C62" s="5" t="n">
         <v>14.1</v>
@@ -18723,6 +18943,26 @@
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>46326</v>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="C63" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D63" s="6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18735,7 +18975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20245,7 +20485,7 @@
         <v>46325</v>
       </c>
       <c r="B75" s="5" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C75" s="5" t="n">
         <v>23.4</v>
@@ -20259,6 +20499,26 @@
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="n">
+        <v>46326</v>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="C76" s="5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="D76" s="6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -20271,7 +20531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21796,6 +22056,26 @@
       </c>
       <c r="F75" t="inlineStr"/>
     </row>
+    <row r="76">
+      <c r="A76" s="4" t="n">
+        <v>46326</v>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="C76" s="5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="D76" s="6" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21807,7 +22087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -23332,6 +23612,26 @@
       </c>
       <c r="F75" t="inlineStr"/>
     </row>
+    <row r="76">
+      <c r="A76" s="4" t="n">
+        <v>46326</v>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="C76" s="5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D76" s="6" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>Pequeno</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
